--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A094C2EC-1A20-4A8C-9B2A-06A795D4125A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D919E2-40F5-4C3D-8ED9-CF0BCDA3ED54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -66,6 +66,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3943,85 +3946,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="38">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4212,6 +4136,48 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4246,6 +4212,43 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4263,9 +4266,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}" name="テーブル1" displayName="テーブル1" ref="A1:C77" totalsRowShown="0">
   <autoFilter ref="A1:C77" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4275,7 +4278,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}" name="テーブル3" displayName="テーブル3" ref="A1:C166" totalsRowShown="0">
   <autoFilter ref="A1:C166" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="34"/>
     <tableColumn id="2" xr3:uid="{AE50F308-AC9C-41D0-959A-F605A2B1244D}" name="Name"/>
     <tableColumn id="3" xr3:uid="{49ACDFEA-EE20-40A5-A482-A6A814586EDF}" name="CardText"/>
   </tableColumns>
@@ -4287,7 +4290,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}" name="テーブル4" displayName="テーブル4" ref="A1:C87" totalsRowShown="0">
   <autoFilter ref="A1:C87" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="33"/>
     <tableColumn id="2" xr3:uid="{267EEC0B-73BC-46B3-94C3-3B4B78AE4646}" name="Name"/>
     <tableColumn id="3" xr3:uid="{C293862E-7AD1-4398-868F-ACAC28AFD4D3}" name="CardText"/>
   </tableColumns>
@@ -4296,10 +4299,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:C94" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="31"/>
     <tableColumn id="1" xr3:uid="{EA68F129-90B0-48A8-AE5B-1AB69A1FED43}" name="Name"/>
     <tableColumn id="2" xr3:uid="{89C4639F-4422-47BF-AD82-8343EBF3FF95}" name="CardText"/>
   </tableColumns>
@@ -4308,12 +4311,12 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C5" totalsRowShown="0" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C5" totalsRowShown="0" dataDxfId="30">
   <autoFilter ref="A1:C5" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -19790,7 +19793,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="56.25">
+    <row r="28" spans="1:3" ht="37.5">
       <c r="A28" s="11">
         <v>2209</v>
       </c>
@@ -26072,7 +26075,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="37.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="13">
         <v>3001</v>
       </c>
@@ -26105,7 +26108,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="56.25">
+    <row r="6" spans="1:3" ht="37.5">
       <c r="A6" s="11">
         <v>3004</v>
       </c>
@@ -26116,7 +26119,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="75">
+    <row r="7" spans="1:3" ht="56.25">
       <c r="A7" s="13">
         <v>3005</v>
       </c>
@@ -26127,7 +26130,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="131.25">
+    <row r="8" spans="1:3" ht="93.75">
       <c r="A8" s="11">
         <v>3006</v>
       </c>
@@ -26215,7 +26218,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="56.25">
+    <row r="16" spans="1:3" ht="37.5">
       <c r="A16" s="11">
         <v>3105</v>
       </c>
@@ -26270,7 +26273,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="56.25">
+    <row r="21" spans="1:3" ht="37.5">
       <c r="A21" s="13">
         <v>3110</v>
       </c>
@@ -26347,7 +26350,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="75">
+    <row r="28" spans="1:3" ht="56.25">
       <c r="A28" s="11">
         <v>3206</v>
       </c>
@@ -26358,7 +26361,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="56.25">
+    <row r="29" spans="1:3" ht="37.5">
       <c r="A29" s="13">
         <v>3207</v>
       </c>

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Shadow\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891E1B7B-BF26-492C-B1D4-59E3F64DE60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA13A12F-7453-44B8-B1BB-44D7AE203C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -8966,62 +8966,28 @@
   <dxfs count="45">
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -9595,6 +9561,65 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
         <patternFill patternType="solid">
@@ -9650,31 +9675,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9692,33 +9692,33 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}" name="テーブル1" displayName="テーブル1" ref="A1:C77" totalsRowShown="0">
   <autoFilter ref="A1:C77" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:C108" xr:uid="{E15C51F9-F521-433C-8765-752424375382}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:C109" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9728,7 +9728,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}" name="テーブル3" displayName="テーブル3" ref="A1:C166" totalsRowShown="0">
   <autoFilter ref="A1:C166" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="44"/>
     <tableColumn id="2" xr3:uid="{AE50F308-AC9C-41D0-959A-F605A2B1244D}" name="Name"/>
     <tableColumn id="3" xr3:uid="{49ACDFEA-EE20-40A5-A482-A6A814586EDF}" name="CardText"/>
   </tableColumns>
@@ -9740,7 +9740,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}" name="テーブル4" displayName="テーブル4" ref="A1:C87" totalsRowShown="0">
   <autoFilter ref="A1:C87" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="43"/>
     <tableColumn id="2" xr3:uid="{267EEC0B-73BC-46B3-94C3-3B4B78AE4646}" name="Name"/>
     <tableColumn id="3" xr3:uid="{C293862E-7AD1-4398-868F-ACAC28AFD4D3}" name="CardText"/>
   </tableColumns>
@@ -9749,10 +9749,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="A1:C94" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="41"/>
     <tableColumn id="1" xr3:uid="{EA68F129-90B0-48A8-AE5B-1AB69A1FED43}" name="Name"/>
     <tableColumn id="2" xr3:uid="{89C4639F-4422-47BF-AD82-8343EBF3FF95}" name="CardText"/>
   </tableColumns>
@@ -9761,60 +9761,60 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C77" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C77" totalsRowShown="0" dataDxfId="40">
   <autoFilter ref="A1:C77" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="36" tableBorderDxfId="35">
   <autoFilter ref="A1:C113" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="32" tableBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A1:C344" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="A1:C126" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:C108" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10308,7 +10308,7 @@
         <v>67</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -10319,7 +10319,7 @@
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -18722,7 +18722,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="56.25">
+    <row r="74" spans="1:3" ht="37.5">
       <c r="A74" s="17">
         <v>4706</v>
       </c>

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FBF257-32B2-4DCD-AB16-DC5F976C66DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD635BA4-C93D-4507-9BEC-53907F383653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -41,15 +41,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="2439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="2493">
   <si>
     <t>フェアリー</t>
     <phoneticPr fontId="1"/>
@@ -12684,6 +12681,540 @@
 【ラストワード】このバトルに勝利する。</t>
     <rPh sb="26" eb="28">
       <t>ショウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場にコスト5以上のニュートラル・フォロワーあるなら、これは+2/+2する。</t>
+    <rPh sb="18" eb="20">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】これは+X/+0する。Xは相手の場の攻撃力最大のフォロワーの攻撃力である。</t>
+    <rPh sb="22" eb="24">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>コウゲキリョクサイダイ</t>
+    </rPh>
+    <rPh sb="39" eb="42">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚か相手のリーダーを選ぶ。それに1ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場にニュートラル・フォロワーが出たとき、それは+1/+0する。</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】相手の場のフォロワー1枚か相手のリーダーを選ぶ。それに1ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『アルティメットキャロット』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】『ミニゴブリンメイジ』1枚を自分の手札に加える。それのコストを0にする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。それを破壊。
+【エンハンス_8】『サタンズサーヴァント』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】相手の場のフォロワー1枚を選ぶ。それに2ダメージ。それがニュートラル・フォロワーなら、2ダメージではなく5ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】場の他のコスト2以上のフォロワーすべてに1ダメージ。場の他のコスト1以下のフォロワーすべてに2ダメージ。</t>
+    <rPh sb="9" eb="10">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札のニュートラル・フォロワー1枚を選ぶ。それを自分の場に出す。それは【突進】と「自分のターン終了時、これを手札に戻す。」を持つ。</t>
+    <rPh sb="36" eb="38">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】場の他のカードすべてを破壊。
+相手の場にフォロワーが2枚以上あるなら、これはリーダーを攻撃できない。</t>
+    <rPh sb="9" eb="10">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ラストワード】『アルティメットキャロット』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【コンボ_3】これは+1/+1する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ラストワード】『精霊の呪い』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『フェアリー』1枚を自分の手札に加える。
+【突進】</t>
+    <rPh sb="31" eb="33">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】これは+X/+0する。Xは自分の手札の枚数である。
+【守護】</t>
+    <rPh sb="36" eb="38">
+      <t>シュゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_6】相手の場のフォロワー1枚を選ぶ。それは『スノーマン』に変身する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それは体力1になる。
+【進化時】相手の場のフォロワー1枚を選ぶ。それに1ダメージ。</t>
+    <rPh sb="28" eb="30">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札のコスト4以下のエルフ・カード1枚を選ぶ。そのコストを0にする。</t>
+    <rPh sb="19" eb="21">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のコスト2以下のフォロワー1枚を選ぶ。それを破壊。【コンボ_3】コスト2以下のフォロワーではなく、コスト5以下のカード。</t>
+    <rPh sb="9" eb="11">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場に他のフォロワーが出たとき、それは【突進】を持つ。</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【コンボ_3】相手の場のフォロワーすべてと相手のリーダーに2ダメージ。
+【守護】</t>
+    <rPh sb="16" eb="18">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>シュゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『飛翔する狩鳥』1枚を自分の場に出す。
+【エンハンス_8】『グランドアーチャー・セルウィン』1枚を自分の手札に加える。それのコストを0にする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・「次の自分のターン開始時」の「次」がいるか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→場で能力を働かせるカードがないなら、クレストにする</t>
+    <rPh sb="1" eb="2">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。ターン終了まで、それは-10/-0する。
+【エンハンス_5】ターン終了まで、それは-10/-0するのではなく破壊。</t>
+    <rPh sb="19" eb="21">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【突進】
+【ラストワード】自分は『クレスト：古き森の白狼』を持つ。
+クレスト
+【カウントダウン_1】
+【ラストワード】自分のデッキから『古き森の白狼』を除くコスト最大のエルフ・カード1枚を引く。それのコストを0にする。</t>
+    <rPh sb="1" eb="3">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のデッキからコスト2のフォロワー1枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場にフォロワーが3枚以上あるなら、これは+1/+1して【必殺】を持つ。</t>
+    <rPh sb="9" eb="11">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>マイイジョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒッサツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【交戦時】自分のデッキから1枚を引く。</t>
+    <rPh sb="1" eb="3">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場に指揮官・カードがあるなら、相手の場のフォロワーすべてに1ダメージ。</t>
+    <rPh sb="30" eb="31">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。それに4ダメージ。
+【エンハンス_8】『ニンジャマスター』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場に指揮官・カードがあるなら、これは+1/+0して【守護】を持つ。</t>
+    <rPh sb="38" eb="40">
+      <t>シュゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_6】これは「【ラストワード】『ナイト』2枚を自分の場に出す。」を持つ。
+【突進】</t>
+    <rPh sb="39" eb="40">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場のフォロワー1枚を選ぶ。他のフォロワーすべてにXダメージ。Xは選んだフォロワーの攻撃力である。</t>
+    <rPh sb="0" eb="2">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『サブリーダー・ゲルト』1枚を自分の手札に加える。相手の場にフォロワーが3枚以上あるなら、それのコストを0にする。</t>
+    <rPh sb="46" eb="47">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【突進】
+【必殺】
+【攻撃時】フォロワーへの攻撃なら、相手のリーダーにXダメージ。Xはこれの攻撃力である。</t>
+    <rPh sb="6" eb="8">
+      <t>ヒッサツ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウゲキジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【カウントダウン_15】
+【ラストワード】自分の場のロイヤル・フォロワーすべては+1/+1して【疾走】を持つ。
+自分のフォロワーが場に出たとき、これの【カウントダウン】を-1する。</t>
+    <rPh sb="21" eb="23">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シッソウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_9】これは「1ターンに2回攻撃できる。」を持つ。ターン終了まで、これは「受ける1以上ダメージを0にする。」を持つ。
+【疾走】</t>
+    <rPh sb="34" eb="36">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>シッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・「受ける1以上ダメージを0にする。」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札の【スペルブースト時】を持つカード1枚を選ぶ。それは2回スペルブーストする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】これが場を離れるまで、自分のリーダーは「受ける1以上のダメージを0にする。」を持つ。</t>
+    <rPh sb="29" eb="30">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【スペルブースト時】これのコストを-1する。
+【疾走】</t>
+    <rPh sb="24" eb="26">
+      <t>シッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のコスト3以下のフォロワー1枚を選ぶ。それを破壊。
+【エンハンス_5】コスト3以下のフォロワーではなく、任意のカード。</t>
+    <rPh sb="26" eb="28">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『土の魔片』1枚を自分の手札に加える。
+【進化時】自分のデッキから【土の秘術】を持つカード1枚を引く。</t>
+    <rPh sb="49" eb="50">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のデッキからアミュレット1枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札すべては2回スペルブーストする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『紅蓮の魔術』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手札で働く。自分のフォロワーが進化したとき、これのコストを1にする。
+相手の場のフォロワー1枚を選ぶ。それと相手のリーダーに2ダメージ。</t>
+    <rPh sb="0" eb="2">
+      <t>テフダ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のターン中、相手の場のフォロワーが破壊されたとき、『ゾンビ』1枚を自分の場に出す。
+自分のターン終了時、【土の秘術_1】相手の場のランダムなフォロワーから1枚を破壊。</t>
+    <rPh sb="11" eb="12">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『マナリアドラコ・グレア』1枚を自分の場に出す。それは進化する。
+【攻撃時】これが進化後なら、相手の場のフォロワーすべてに1ダメージ。</t>
+    <rPh sb="36" eb="38">
+      <t>シンカ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>コウゲキジ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>シンカゴ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のランダムなフォロワーから1枚に5ダメージ。
+【エンハンス_9】ダメージを与えるのではなく、『アークサモナー・エラスムス』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【スペルブースト時】これのコストを-1する。
+【ファンファーレ】自分の手札をすべて消滅。自分のデッキから5枚を引く。自分の手札すべては5回スペルブーストする。</t>
+    <rPh sb="32" eb="34">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>テフダ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ショウメツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -17952,7 +18483,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24FCBE1-754C-45D2-B30B-7C4BA5B12A85}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -18116,11 +18647,17 @@
       <c r="A21" t="s">
         <v>2177</v>
       </c>
+      <c r="L21" t="s">
+        <v>2463</v>
+      </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>2209</v>
       </c>
+      <c r="L22" t="s">
+        <v>2464</v>
+      </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
@@ -18140,6 +18677,11 @@
     <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>2321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>2479</v>
       </c>
     </row>
   </sheetData>
@@ -29371,7 +29913,8 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="153.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -29393,7 +29936,7 @@
         <v>1521</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1521</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -29404,7 +29947,7 @@
         <v>1522</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>1522</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -29415,7 +29958,7 @@
         <v>1523</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>1523</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -29426,7 +29969,7 @@
         <v>1524</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>1524</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -29437,7 +29980,7 @@
         <v>1525</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>1525</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -29448,7 +29991,7 @@
         <v>1526</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>1526</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -29459,7 +30002,7 @@
         <v>1527</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>1527</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -29470,18 +30013,18 @@
         <v>1528</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="37.5">
       <c r="A10" s="12">
         <v>103008</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>1529</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>1529</v>
+      <c r="C10" s="25" t="s">
+        <v>2446</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -29492,7 +30035,7 @@
         <v>1530</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>1530</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -29503,7 +30046,7 @@
         <v>1531</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>1531</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -29514,7 +30057,7 @@
         <v>1532</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>1532</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -29525,18 +30068,18 @@
         <v>1533</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="37.5">
       <c r="A15" s="12">
         <v>103013</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>1534</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>1534</v>
+      <c r="C15" s="25" t="s">
+        <v>2450</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -29547,7 +30090,7 @@
         <v>1535</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>1535</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -29558,7 +30101,7 @@
         <v>1536</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>1536</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -29569,40 +30112,40 @@
         <v>1537</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="37.5">
       <c r="A19" s="12">
         <v>103102</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>1538</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="C19" s="25" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="37.5">
       <c r="A20" s="12">
         <v>103103</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>1539</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="C20" s="25" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="37.5">
       <c r="A21" s="12">
         <v>103104</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>1540</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>1540</v>
+      <c r="C21" s="25" t="s">
+        <v>2465</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -29613,18 +30156,18 @@
         <v>1541</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="37.5">
       <c r="A23" s="12">
         <v>103106</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>1542</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>1542</v>
+      <c r="C23" s="25" t="s">
+        <v>2457</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -29635,7 +30178,7 @@
         <v>1543</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>1543</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -29646,7 +30189,7 @@
         <v>1544</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>1544</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -29657,40 +30200,40 @@
         <v>1545</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="37.5">
       <c r="A27" s="12">
         <v>103110</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>1546</v>
       </c>
-      <c r="C27" s="19" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="C27" s="25" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="37.5">
       <c r="A28" s="12">
         <v>103111</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>1547</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="C28" s="25" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="93.75">
       <c r="A29" s="12">
         <v>103112</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>1548</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>1548</v>
+      <c r="C29" s="25" t="s">
+        <v>2466</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -29701,7 +30244,7 @@
         <v>1549</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>1549</v>
+        <v>990</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -29712,7 +30255,7 @@
         <v>1550</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1550</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -29723,7 +30266,7 @@
         <v>1551</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>1551</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -29734,7 +30277,7 @@
         <v>1552</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>1552</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -29745,18 +30288,18 @@
         <v>1553</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>1553</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="37.5">
       <c r="A35" s="12">
         <v>103204</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>1554</v>
       </c>
-      <c r="C35" s="19" t="s">
-        <v>1554</v>
+      <c r="C35" s="25" t="s">
+        <v>2471</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -29767,18 +30310,18 @@
         <v>1555</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>1555</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="37.5">
       <c r="A37" s="12">
         <v>103206</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>1556</v>
       </c>
-      <c r="C37" s="19" t="s">
-        <v>1556</v>
+      <c r="C37" s="25" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -29789,7 +30332,7 @@
         <v>1557</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1557</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -29800,7 +30343,7 @@
         <v>1558</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>1558</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -29811,40 +30354,40 @@
         <v>1559</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>1559</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="56.25">
       <c r="A41" s="12">
         <v>103210</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>1560</v>
       </c>
-      <c r="C41" s="19" t="s">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="C41" s="25" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="56.25">
       <c r="A42" s="12">
         <v>103211</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>1561</v>
       </c>
-      <c r="C42" s="19" t="s">
-        <v>1561</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="C42" s="25" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="37.5">
       <c r="A43" s="12">
         <v>103212</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>1562</v>
       </c>
-      <c r="C43" s="19" t="s">
-        <v>1562</v>
+      <c r="C43" s="25" t="s">
+        <v>2478</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -29855,7 +30398,7 @@
         <v>1563</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>1563</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -29866,7 +30409,7 @@
         <v>1564</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>1564</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -29877,40 +30420,40 @@
         <v>1565</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>1565</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="37.5">
       <c r="A47" s="12">
         <v>103303</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>1566</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="C47" s="25" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="37.5">
       <c r="A48" s="12">
         <v>103304</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>1567</v>
       </c>
-      <c r="C48" s="19" t="s">
-        <v>1567</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="C48" s="25" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="37.5">
       <c r="A49" s="12">
         <v>103305</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>1568</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>1568</v>
+      <c r="C49" s="25" t="s">
+        <v>2484</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -29921,7 +30464,7 @@
         <v>1569</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>1569</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -29932,62 +30475,62 @@
         <v>1570</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="37.5">
       <c r="A52" s="12">
         <v>103308</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>1571</v>
       </c>
-      <c r="C52" s="19" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="C52" s="25" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="37.5">
       <c r="A53" s="12">
         <v>103309</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>1572</v>
       </c>
-      <c r="C53" s="19" t="s">
-        <v>1572</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="C53" s="25" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="37.5">
       <c r="A54" s="12">
         <v>103310</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>1573</v>
       </c>
-      <c r="C54" s="19" t="s">
-        <v>1573</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="C54" s="25" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="37.5">
       <c r="A55" s="12">
         <v>103311</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>1574</v>
       </c>
-      <c r="C55" s="19" t="s">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="C55" s="25" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="37.5">
       <c r="A56" s="12">
         <v>103312</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>1575</v>
       </c>
-      <c r="C56" s="19" t="s">
-        <v>1575</v>
+      <c r="C56" s="25" t="s">
+        <v>2492</v>
       </c>
     </row>
     <row r="57" spans="1:3">

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD635BA4-C93D-4507-9BEC-53907F383653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081E1AC0-AA3B-4AD1-8EC6-4542BCA22D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -41,12 +41,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="2493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="2549">
   <si>
     <t>フェアリー</t>
     <phoneticPr fontId="1"/>
@@ -8592,20 +8595,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【ファンファーレ】【覚醒】なら、これは【守護】を持つ。</t>
-    <rPh sb="20" eb="22">
-      <t>シュゴ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【ファンファーレ】【覚醒】なら、これは+2/+0する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】自分のリーダーを2回復。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -9049,13 +9038,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>自分の場の他の攻撃力1のフォロワーが攻撃するとき、相手のリーダーに1ダメージ。</t>
-    <rPh sb="3" eb="4">
-      <t>バ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】自分の場の他のカード1枚を選ぶ。それを手札に戻す。
 【守護】</t>
     <phoneticPr fontId="1"/>
@@ -9133,22 +9115,6 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>タイリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相手の場のフォロワーが攻撃するとき、相手のターンなら、それに1ダメージ。</t>
-    <rPh sb="0" eb="2">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>アイテ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9174,16 +9140,6 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>マイスウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・「【覚醒】なら、+1/+0する。」のような、タイミングがない能力</t>
-    <rPh sb="3" eb="5">
-      <t>カクセイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ノウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10559,19 +10515,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>→これだけ昔の能力っぽいから【ファンファーレ】に統一する。</t>
-    <rPh sb="5" eb="6">
-      <t>ムカシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ノウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>トウイツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>→基本的に「これが進化後なら〇〇」に統一。長くなる場合は変更。</t>
     <rPh sb="1" eb="4">
       <t>キホンテキ</t>
@@ -10595,21 +10538,6 @@
   </si>
   <si>
     <t>【ファンファーレ】【覚醒】なら、自分のデッキから1枚を引く。自分のPP最大値を+1する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【ファンファーレ】【覚醒】なら、これは+3/+0する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【ファンファーレ】【覚醒】なら、これは【威圧】を持つ。
-【疾走】</t>
-    <rPh sb="10" eb="12">
-      <t>カクセイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>モ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -11344,31 +11272,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>相手のターン中、これは+1/+0する。</t>
-    <rPh sb="0" eb="2">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>チュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】自分の場の【カウントダウン】を持つアミュレット1枚を選ぶ。それは【カウントダウン】を-1する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相手のターン中、これは【必殺】を持つ。</t>
-    <rPh sb="12" eb="14">
-      <t>ヒッサツ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相手のターン中、これは+2/+0する。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -11437,23 +11341,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【守護】
-相手のターン中、受けるダメージを-1する。</t>
-    <rPh sb="1" eb="3">
-      <t>シュゴ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】自分のデッキから【カウントダウン】を持つアミュレット1枚を引く。</t>
     <rPh sb="27" eb="28">
       <t>モ</t>
@@ -11489,14 +11376,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【守護】
-相手のターン中、これは+4/+0する。</t>
-    <rPh sb="1" eb="3">
-      <t>シュゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】自分の場のフォロワーすべては【オーラ】を持つ。</t>
     <rPh sb="9" eb="11">
       <t>ジブン</t>
@@ -11559,25 +11438,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>→わかりずら過ぎるから、この能力だけ、タイミング指定なしの「これが場にある限り」</t>
-    <rPh sb="6" eb="7">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ノウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>カギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>これが場にある限り、自分の場のフォロワーすべては「攻撃力ではなく体力と同じダメージを与える」を持つ。</t>
     <rPh sb="3" eb="4">
       <t>バ</t>
@@ -11590,25 +11450,6 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>バ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相手のターン中、相手の場のフォロワーが攻撃するとき、それは-2/-0する。</t>
-    <rPh sb="0" eb="2">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>チュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -12240,13 +12081,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>相手の場の体力3以下のフォロワー1枚を選ぶ。それを破壊。【ネクロマンス_4】体力3以下のフォロワーではなく任意のフォロワー。</t>
-    <rPh sb="53" eb="55">
-      <t>ニンイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・条件によって、「○○ではなく○○」の後者がない場合。</t>
     <rPh sb="1" eb="3">
       <t>ジョウケン</t>
@@ -12516,19 +12350,6 @@
     </rPh>
     <rPh sb="113" eb="115">
       <t>ハカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これが場にある限り、自分のリーダーは「自分のターン中、自分のリーダーがダメージを受けるなら、自分のリーダーではなく相手のリーダーが受ける。」を持つ。</t>
-    <rPh sb="3" eb="4">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カギ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジブン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -13100,22 +12921,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>【ファンファーレ】これが場を離れるまで、自分のリーダーは「受ける1以上のダメージを0にする。」を持つ。</t>
-    <rPh sb="29" eb="30">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【スペルブースト時】これのコストを-1する。
 【疾走】</t>
     <rPh sb="24" eb="26">
@@ -13166,23 +12971,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>自分のターン中、相手の場のフォロワーが破壊されたとき、『ゾンビ』1枚を自分の場に出す。
-自分のターン終了時、【土の秘術_1】相手の場のランダムなフォロワーから1枚を破壊。</t>
-    <rPh sb="11" eb="12">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>アイテ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="80" eb="81">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>【ファンファーレ】『マナリアドラコ・グレア』1枚を自分の場に出す。それは進化する。
 【攻撃時】これが進化後なら、相手の場のフォロワーすべてに1ダメージ。</t>
     <rPh sb="36" eb="38">
@@ -13215,6 +13003,661 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>ショウメツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【覚醒】なら、自分の場のフォロワー1枚を選ぶ。それは+1/+1する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これが捨てられたとき、『煌牙の戦士・キット』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それに2ダメージ。自分の手札のコスト最小のカードからランダム1枚を捨てる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ラストワード】『ブレイジングブレス』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】これが場を離れるまで、自分のリーダーは「受ける1以上のダメージを0にする。」を持つ。</t>
+    <rPh sb="16" eb="17">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イジョウモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→わかりずら過ぎるから、この能力だけ、タイミング指定なしの「これが場にある限り」。ファンファーレ付与なら「これが場を離れるまで」</t>
+    <rPh sb="6" eb="7">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これが場にある限り、自分のリーダーは「与えるダメージを+1する。」を持つ。</t>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_7】これは+2/+2して【疾走】を持つ。
+【威圧】</t>
+    <rPh sb="20" eb="22">
+      <t>シッソウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>イアツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】「自分の手札のコスト最小のカードからランダム1枚を捨てる。」を2回行う。
+【ラストワード】自分のデッキから3枚を引く。</t>
+    <rPh sb="41" eb="43">
+      <t>カイオコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+【進化時】相手の場のフォロワー1枚を選ぶ。それに5ダメージ。自分の手札のコスト最小のカードからランダム1枚を捨てる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のPP最大値を+1する。自分のデッキから2枚を引く。自分のリーダーを3回復。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_7】これは+3/+3して【突進】と【必殺】を持つ。</t>
+    <rPh sb="20" eb="22">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒッサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『プリンセスマナリア・アン』1枚を自分の場に出す。それは進化する。
+これが進化後なら、1ターンに2回攻撃できる。</t>
+    <rPh sb="46" eb="49">
+      <t>シンカゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。それに3ダメージ。
+【エンハンス_6】相手の場のフォロワーすべてに2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札をすべて捨てる。相手の場のフォロワーすべてと相手のリーダーにXダメージ。Xはこれで捨てた枚数である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・「したとき」と表せない、するときに挙動が変わる場合</t>
+    <rPh sb="8" eb="9">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【ネクロマンス_4】相手の場のフォロワー1枚を選ぶ。それに2ダメージ。
+【守護】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ラストワード】『リッチ』1枚を自分の場に出す。
+【守護】を持たないフォロワーを攻撃できない。</t>
+    <rPh sb="26" eb="28">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【ネクロマンス_2】これは「【ラストワード】『ゾンビ』1枚を自分の場に出す。」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『ゴースト』2枚を自分の場に出す。
+【エンハンス_8】それは【必殺】を持つ。</t>
+    <rPh sb="31" eb="33">
+      <t>ヒッサツ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ラストワード】相手の場のフォロワーからランダム1枚を破壊。
+【守護】を持たないフォロワーを攻撃できない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場の他のフォロワー1枚を選ぶ。選んだなら、それを破壊。相手の場のフォロワーからランダム1枚を破壊。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+【ラストワード】相手の場の攻撃力最大のフォロワーからランダム1枚を破壊。自分のリーダーをX回復。Xは相手の場の攻撃力最大のフォロワーの攻撃力である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場の体力3以下のフォロワー1枚を選ぶ。それを破壊。自分の墓場が4枚以上あるなら、体力3以下のフォロワーではなく任意のフォロワー。【ネクロマンス_4】それを破壊。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場の体力1のフォロワー1枚を選ぶ。それを破壊。自分の墓場が8枚以上あるなら、体力1のフォロワーではなく任意のフォロワー。【ネクロマンス_8】それを破壊。</t>
+    <rPh sb="54" eb="56">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手のターン終了まで、これは【潜伏】を持つ。
+自分の他のフォロワーが破壊されたとき、これは+1/+1する。</t>
+    <rPh sb="24" eb="26">
+      <t>センプク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【必殺】
+【ラストワード】相手の場のフォロワーすべてに3ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場の体力4以下のフォロワー1枚を選ぶ。それを破壊。
+【エンハンス_7】『プルート』1枚を自分の場に出す。それを+X/+Yする。X/Yは選んだフォロワーの攻撃力/体力である。</t>
+    <rPh sb="8" eb="10">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手のフォロワーが場に出たとき、相手のリーダーに1ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【復讐】なら、『人狼の群れ長』1枚を自分の場に出す。
+【必殺】</t>
+    <rPh sb="37" eb="39">
+      <t>ヒッサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【復讐】なら、自分のEPを1回復。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のターン終了時、自分のリーダーに2ダメージを与える。これは+2/+0する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場の他のフォロワー1枚を選ぶ。それは【突進】を持つ。
+【エンハンス_4】それは+2/+2する。</t>
+    <rPh sb="22" eb="24">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+【交戦時】『フォレストバット』1枚を自分の場に出す。</t>
+    <rPh sb="6" eb="9">
+      <t>コウセンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【復讐】なら、相手の場のフォロワー1枚を選ぶ。それに2ダメージ。
+【進化時】相手の場のフォロワー1枚を選ぶ。それに2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【交戦時】相手の場のフォロワーすべてに1ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。相手の場のそれと同名のフォロワーすべてに3ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【必殺】
+【守護】を持たないフォロワーを攻撃できない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【突進】
+【攻撃時】相手のフォロワーへの攻撃で交戦相手を破壊してこれが破壊されなかったなら、自分のデッキから1枚を引く。</t>
+    <rPh sb="23" eb="27">
+      <t>コウセンアイテ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のリーダーに2ダメージ。相手の場のフォロワー1枚を選ぶ。それに6ダメージ。
+【エンハンス_7】『ビーストドミネーター』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワーすべてに2ダメージ。
+相手の場のフォロワーが破壊されたとき、相手のリーダーに1ダメージ。</t>
+    <rPh sb="30" eb="32">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_4】自分の場のフォロワー1枚か自分のリーダーを選ぶ。それを3回復。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のターン終了時、自分の場のアミュレットすべての【カウントダウン】を-1する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『詠唱：聖獣への誓い』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『詠唱：死の宣告』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のデッキのフォロワーからそれぞれコストの異なるランダムX枚を自分の場に出す。Xは場の上限枚数から自分の場のカードの枚数を引いた値である。それを破壊。</t>
+    <rPh sb="82" eb="84">
+      <t>ハカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のデッキのコスト2以下の【カウントダウン】を持つアミュレットからそれぞれ名前の異なるランダム3枚を自分の場に出す。</t>
+    <rPh sb="11" eb="13">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・「それぞれ○○の異なる○枚を場に出す。」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→「自分のデッキの○○からそれぞれ○○の異なるランダム3枚を自分の場に出す。」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【交戦時】相手のリーダーに1ダメージ。
+【進化時】【交戦時】と同じ能力が働く。</t>
+    <rPh sb="31" eb="32">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+相手のターンなら、これは+4/+0する。</t>
+    <rPh sb="1" eb="3">
+      <t>シュゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手のターンなら、これは+2/+0する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手のターンなら、これは【必殺】を持つ。</t>
+    <rPh sb="13" eb="15">
+      <t>ヒッサツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手のターンなら、これは+1/+0する。</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これが場にある限り、自分のリーダーは「自分のリーダーがダメージを受けたとき、自分のターンなら、自分のリーダーではなく相手のリーダーが受ける。」を持つ。</t>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・「【覚醒】なら、+1/+0する。」「相手のターン中なら」のような、タイミングがない能力</t>
+    <rPh sb="3" eb="5">
+      <t>カクセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→条件に起こすと複雑すぎるから変更なし</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フクザツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワーが破壊されたとき、自分のターンなら、『ゾンビ』1枚を自分の場に出す。
+自分のターン終了時、【土の秘術_1】相手の場のランダムなフォロワーから1枚を破壊。</t>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手のフォロワーが攻撃したとき、それは「ターン終了時、これを破壊。」を持つ。</t>
+    <rPh sb="9" eb="11">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハカイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【覚醒】なら、これは+3/+0する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【疾走】
+【覚醒】なら、これは【威圧】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【覚醒】なら、これは+2/+0する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【覚醒】なら、これは【守護】を持つ。</t>
+    <rPh sb="11" eb="13">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+相手のターンなら、「受けるダメージを-1。」を持つ。</t>
+    <rPh sb="1" eb="3">
+      <t>シュゴ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワーが攻撃したとき、それは-2/-0する。</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワーが攻撃したとき、それに1ダメージ。</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場の他の攻撃力1のフォロワーが攻撃したとき、相手のリーダーに1ダメージ。</t>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場の他のフォロワーすべては「これが消滅したとき、消滅ではなく破壊。」を持つ。
+自分のフォロワーが場に出たとき、それは「これが消滅したとき、消滅ではなく破壊。」を持つ。</t>
+    <rPh sb="9" eb="15">
+      <t>ジブンノバノホカ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→「したとき」でごり押し</t>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】相手の場のフォロワーすべてに2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【カウントダウン_4】
+自分のターン終了時、自分の場のフォロワーすべてと自分のリーダーを1回復。</t>
+    <rPh sb="25" eb="26">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場の他のフォロワー1枚を選ぶ。それは+3/+3して【突進】を持つ。</t>
+    <rPh sb="38" eb="40">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【突進】
+受ける4以上のダメージを3にする。</t>
+    <rPh sb="1" eb="3">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【カウントダウン_3】
+【ファンファーレ】相手の場のフォロワーからランダム1枚を破壊。
+【ラストワード】【ファンファーレ】と同じ能力が働く。</t>
+    <rPh sb="62" eb="63">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ハタラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【威圧】
+フォロワーやリーダーを攻撃できない。
+自分のターン開始時、これは進化する。
+自分のターン終了時、これが進化後なら、自分の場のアミュレットすべてを破壊。</t>
+    <rPh sb="1" eb="3">
+      <t>イアツ</t>
+    </rPh>
+    <rPh sb="56" eb="59">
+      <t>シンカゴ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>バ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -18496,7 +18939,7 @@
         <v>973</v>
       </c>
       <c r="L2" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -18504,7 +18947,7 @@
         <v>974</v>
       </c>
       <c r="L3" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -18512,7 +18955,7 @@
         <v>975</v>
       </c>
       <c r="L4" t="s">
-        <v>2309</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -18520,7 +18963,7 @@
         <v>976</v>
       </c>
       <c r="L5" t="s">
-        <v>2057</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -18528,7 +18971,7 @@
         <v>977</v>
       </c>
       <c r="L6" t="s">
-        <v>2188</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -18536,7 +18979,7 @@
         <v>978</v>
       </c>
       <c r="L7" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -18544,7 +18987,7 @@
         <v>979</v>
       </c>
       <c r="L8" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -18552,136 +18995,148 @@
         <v>980</v>
       </c>
       <c r="L9" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="L10" t="s">
-        <v>2189</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="L11" t="s">
-        <v>2236</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="L12" t="s">
-        <v>2238</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="L13" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="L14" t="s">
-        <v>2278</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="L15" t="s">
-        <v>2391</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="L16" t="s">
-        <v>2392</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="L17" t="s">
-        <v>2399</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="L18" t="s">
-        <v>2400</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="L19" t="s">
-        <v>2434</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="L20" t="s">
-        <v>2435</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="L21" t="s">
-        <v>2463</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>2209</v>
+        <v>2201</v>
       </c>
       <c r="L22" t="s">
-        <v>2464</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>2210</v>
+        <v>2202</v>
+      </c>
+      <c r="L23" t="s">
+        <v>2489</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>2230</v>
+        <v>2222</v>
+      </c>
+      <c r="L24" t="s">
+        <v>2542</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>2275</v>
+        <v>2267</v>
+      </c>
+      <c r="L25" t="s">
+        <v>2521</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>2321</v>
+        <v>2306</v>
+      </c>
+      <c r="L26" t="s">
+        <v>2522</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>2479</v>
+        <v>2462</v>
       </c>
     </row>
   </sheetData>
@@ -23529,7 +23984,7 @@
         <v>871</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="37.5">
@@ -23540,7 +23995,7 @@
         <v>872</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="37.5">
@@ -23551,7 +24006,7 @@
         <v>873</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -23661,7 +24116,7 @@
         <v>883</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -23771,7 +24226,7 @@
         <v>892</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -23991,7 +24446,7 @@
         <v>910</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>1995</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -24002,7 +24457,7 @@
         <v>911</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1994</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -24024,7 +24479,7 @@
         <v>913</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -24035,7 +24490,7 @@
         <v>914</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>2155</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -24057,7 +24512,7 @@
         <v>916</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>2190</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -24398,7 +24853,7 @@
         <v>946</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>2421</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -24574,7 +25029,7 @@
         <v>962</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -24748,7 +25203,7 @@
         <v>1058</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -24770,7 +25225,7 @@
         <v>1060</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -24781,7 +25236,7 @@
         <v>1061</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -24803,7 +25258,7 @@
         <v>1063</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="37.5">
@@ -24814,7 +25269,7 @@
         <v>1064</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="37.5">
@@ -24825,7 +25280,7 @@
         <v>1065</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -24858,7 +25313,7 @@
         <v>1068</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -24869,7 +25324,7 @@
         <v>1069</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -24880,7 +25335,7 @@
         <v>1070</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -24891,7 +25346,7 @@
         <v>1071</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="37.5">
@@ -24902,7 +25357,7 @@
         <v>1072</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -24913,7 +25368,7 @@
         <v>1073</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -24924,7 +25379,7 @@
         <v>1074</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -24935,7 +25390,7 @@
         <v>1075</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -24946,7 +25401,7 @@
         <v>1076</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -24957,7 +25412,7 @@
         <v>1077</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -24968,7 +25423,7 @@
         <v>1078</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -25012,7 +25467,7 @@
         <v>1082</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -25023,7 +25478,7 @@
         <v>1083</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -25034,7 +25489,7 @@
         <v>1084</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -25056,7 +25511,7 @@
         <v>1086</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -25067,7 +25522,7 @@
         <v>1087</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -25078,7 +25533,7 @@
         <v>1088</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -25089,7 +25544,7 @@
         <v>1089</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -25100,7 +25555,7 @@
         <v>1090</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -25111,7 +25566,7 @@
         <v>1091</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -25122,7 +25577,7 @@
         <v>1092</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -25133,7 +25588,7 @@
         <v>1093</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -25155,7 +25610,7 @@
         <v>1095</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -25166,7 +25621,7 @@
         <v>1096</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -25177,7 +25632,7 @@
         <v>1097</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -25188,7 +25643,7 @@
         <v>1098</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="37.5">
@@ -25199,7 +25654,7 @@
         <v>1099</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -25210,7 +25665,7 @@
         <v>1100</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -25221,7 +25676,7 @@
         <v>1101</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="37.5">
@@ -25232,7 +25687,7 @@
         <v>1102</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -25243,7 +25698,7 @@
         <v>1103</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -25254,7 +25709,7 @@
         <v>1104</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -25265,7 +25720,7 @@
         <v>1105</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -25276,7 +25731,7 @@
         <v>1106</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>2042</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="37.5">
@@ -25287,7 +25742,7 @@
         <v>1107</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -25298,7 +25753,7 @@
         <v>1108</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -25309,7 +25764,7 @@
         <v>1109</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -25320,7 +25775,7 @@
         <v>1110</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -25331,7 +25786,7 @@
         <v>1111</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -25342,7 +25797,7 @@
         <v>1112</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -25353,7 +25808,7 @@
         <v>1113</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="37.5">
@@ -25375,7 +25830,7 @@
         <v>1115</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -25386,7 +25841,7 @@
         <v>1116</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -25397,7 +25852,7 @@
         <v>1117</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>2053</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="37.5">
@@ -25408,7 +25863,7 @@
         <v>1118</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -25419,7 +25874,7 @@
         <v>1119</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -25430,7 +25885,7 @@
         <v>1120</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -25441,7 +25896,7 @@
         <v>1121</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>2056</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -25452,7 +25907,7 @@
         <v>1122</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="37.5">
@@ -25463,7 +25918,7 @@
         <v>1123</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -25474,7 +25929,7 @@
         <v>1124</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -25485,7 +25940,7 @@
         <v>1125</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -25529,7 +25984,7 @@
         <v>1129</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -25540,7 +25995,7 @@
         <v>1130</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -25562,7 +26017,7 @@
         <v>1132</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -25584,7 +26039,7 @@
         <v>1134</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -25606,7 +26061,7 @@
         <v>1136</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -25617,7 +26072,7 @@
         <v>1137</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -25628,7 +26083,7 @@
         <v>1138</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -25650,7 +26105,7 @@
         <v>1140</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -25661,7 +26116,7 @@
         <v>1141</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -25672,7 +26127,7 @@
         <v>1142</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -25683,7 +26138,7 @@
         <v>1143</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -25694,7 +26149,7 @@
         <v>1144</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -25705,7 +26160,7 @@
         <v>1145</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -25716,7 +26171,7 @@
         <v>1146</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -25727,7 +26182,7 @@
         <v>1147</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -25738,7 +26193,7 @@
         <v>1148</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -25749,7 +26204,7 @@
         <v>1149</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -25760,7 +26215,7 @@
         <v>1150</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -25771,7 +26226,7 @@
         <v>1151</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -25782,7 +26237,7 @@
         <v>1152</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -25793,7 +26248,7 @@
         <v>1153</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -25804,7 +26259,7 @@
         <v>1154</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -25815,7 +26270,7 @@
         <v>1155</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -25826,7 +26281,7 @@
         <v>1156</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -25837,7 +26292,7 @@
         <v>1157</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -25848,7 +26303,7 @@
         <v>1158</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -25859,7 +26314,7 @@
         <v>1159</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="37.5">
@@ -25870,7 +26325,7 @@
         <v>1160</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="37.5">
@@ -25892,7 +26347,7 @@
         <v>1162</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>2101</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -25903,7 +26358,7 @@
         <v>1163</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -25914,7 +26369,7 @@
         <v>1164</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="37.5">
@@ -25925,7 +26380,7 @@
         <v>1165</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -25936,7 +26391,7 @@
         <v>1166</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -25947,7 +26402,7 @@
         <v>1167</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>2229</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="37.5">
@@ -25958,7 +26413,7 @@
         <v>1168</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -26013,7 +26468,7 @@
         <v>1173</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -26024,7 +26479,7 @@
         <v>1174</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -26035,7 +26490,7 @@
         <v>1175</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -26046,7 +26501,7 @@
         <v>1176</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -26057,7 +26512,7 @@
         <v>1177</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -26068,7 +26523,7 @@
         <v>1178</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -26079,7 +26534,7 @@
         <v>1179</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -26090,7 +26545,7 @@
         <v>1180</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -26101,7 +26556,7 @@
         <v>1181</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -26112,7 +26567,7 @@
         <v>1182</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -26123,7 +26578,7 @@
         <v>1183</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -26134,7 +26589,7 @@
         <v>1184</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="37.5">
@@ -26145,7 +26600,7 @@
         <v>1185</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -26156,7 +26611,7 @@
         <v>1186</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="37.5">
@@ -26167,7 +26622,7 @@
         <v>1187</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="37.5">
@@ -26178,7 +26633,7 @@
         <v>1188</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="37.5">
@@ -26189,7 +26644,7 @@
         <v>1189</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -26200,7 +26655,7 @@
         <v>1190</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -26211,7 +26666,7 @@
         <v>1191</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -26222,7 +26677,7 @@
         <v>1192</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="56.25">
@@ -26233,7 +26688,7 @@
         <v>1193</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -26244,7 +26699,7 @@
         <v>1194</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="37.5">
@@ -26255,7 +26710,7 @@
         <v>1195</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -26266,7 +26721,7 @@
         <v>1196</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -26277,7 +26732,7 @@
         <v>1197</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -26288,7 +26743,7 @@
         <v>1198</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -26299,7 +26754,7 @@
         <v>1199</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -26310,7 +26765,7 @@
         <v>1200</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -26321,7 +26776,7 @@
         <v>1201</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="37.5">
@@ -26332,7 +26787,7 @@
         <v>1202</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -26343,7 +26798,7 @@
         <v>1203</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -26354,7 +26809,7 @@
         <v>1204</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -26365,7 +26820,7 @@
         <v>1205</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>2136</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="56.25">
@@ -26376,7 +26831,7 @@
         <v>1206</v>
       </c>
       <c r="C152" s="17" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -26387,7 +26842,7 @@
         <v>1207</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="56.25">
@@ -26398,7 +26853,7 @@
         <v>1208</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="37.5">
@@ -26409,7 +26864,7 @@
         <v>1209</v>
       </c>
       <c r="C155" s="17" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -26420,7 +26875,7 @@
         <v>1210</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="56.25">
@@ -26431,7 +26886,7 @@
         <v>1211</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="37.5">
@@ -26442,7 +26897,7 @@
         <v>1212</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -26453,7 +26908,7 @@
         <v>1213</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="56.25">
@@ -26464,7 +26919,7 @@
         <v>1214</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -26486,7 +26941,7 @@
         <v>1215</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -26497,7 +26952,7 @@
         <v>1216</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -26508,7 +26963,7 @@
         <v>1217</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -26519,7 +26974,7 @@
         <v>1218</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -26530,7 +26985,7 @@
         <v>1219</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -26541,7 +26996,7 @@
         <v>1220</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -26574,7 +27029,7 @@
         <v>1223</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -26585,7 +27040,7 @@
         <v>1224</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>2191</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -26596,7 +27051,7 @@
         <v>1225</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>2156</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -26607,7 +27062,7 @@
         <v>1226</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -26640,7 +27095,7 @@
         <v>1229</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -26651,7 +27106,7 @@
         <v>1230</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -26684,7 +27139,7 @@
         <v>1233</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -26695,7 +27150,7 @@
         <v>1234</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -26706,7 +27161,7 @@
         <v>1235</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -26717,7 +27172,7 @@
         <v>1236</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -26728,7 +27183,7 @@
         <v>1237</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="37.5">
@@ -26739,7 +27194,7 @@
         <v>1238</v>
       </c>
       <c r="C185" s="17" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -26750,7 +27205,7 @@
         <v>1239</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -26761,7 +27216,7 @@
         <v>1240</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -26772,7 +27227,7 @@
         <v>1241</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>2280</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -26783,7 +27238,7 @@
         <v>1242</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -26794,7 +27249,7 @@
         <v>1243</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -26805,7 +27260,7 @@
         <v>1244</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -26816,7 +27271,7 @@
         <v>1245</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -26827,7 +27282,7 @@
         <v>1246</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -26838,7 +27293,7 @@
         <v>1247</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -26849,7 +27304,7 @@
         <v>1248</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="37.5">
@@ -26860,7 +27315,7 @@
         <v>1249</v>
       </c>
       <c r="C196" s="17" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -26871,7 +27326,7 @@
         <v>1250</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="37.5">
@@ -26882,7 +27337,7 @@
         <v>1251</v>
       </c>
       <c r="C198" s="17" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -26893,7 +27348,7 @@
         <v>1252</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -26904,7 +27359,7 @@
         <v>1253</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -26915,7 +27370,7 @@
         <v>1254</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -26937,7 +27392,7 @@
         <v>1256</v>
       </c>
       <c r="C203" s="17" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -26948,7 +27403,7 @@
         <v>1257</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="37.5">
@@ -26959,7 +27414,7 @@
         <v>1258</v>
       </c>
       <c r="C205" s="17" t="s">
-        <v>2192</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="56.25">
@@ -26970,7 +27425,7 @@
         <v>1259</v>
       </c>
       <c r="C206" s="17" t="s">
-        <v>2193</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -26981,7 +27436,7 @@
         <v>1260</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>2194</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -27014,7 +27469,7 @@
         <v>1263</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>2195</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -27025,7 +27480,7 @@
         <v>1264</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>2196</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -27047,7 +27502,7 @@
         <v>1266</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>2197</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -27080,7 +27535,7 @@
         <v>1269</v>
       </c>
       <c r="C216" s="11" t="s">
-        <v>2198</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -27091,7 +27546,7 @@
         <v>1270</v>
       </c>
       <c r="C217" s="11" t="s">
-        <v>2199</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -27102,7 +27557,7 @@
         <v>1271</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>2200</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -27113,7 +27568,7 @@
         <v>1272</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>2201</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -27124,7 +27579,7 @@
         <v>1273</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>2202</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -27135,7 +27590,7 @@
         <v>1274</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>2203</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -27146,7 +27601,7 @@
         <v>1275</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>2204</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -27168,7 +27623,7 @@
         <v>1277</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -27179,7 +27634,7 @@
         <v>1278</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>2206</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -27190,7 +27645,7 @@
         <v>1279</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -27201,7 +27656,7 @@
         <v>1280</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>2211</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -27212,7 +27667,7 @@
         <v>1281</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>2212</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -27223,7 +27678,7 @@
         <v>1282</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>2213</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -27234,7 +27689,7 @@
         <v>1283</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>2214</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -27245,7 +27700,7 @@
         <v>1284</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>2215</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -27256,7 +27711,7 @@
         <v>1285</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>2216</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -27267,7 +27722,7 @@
         <v>1286</v>
       </c>
       <c r="C233" s="11" t="s">
-        <v>2217</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -27278,7 +27733,7 @@
         <v>1287</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>2218</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -27289,7 +27744,7 @@
         <v>1288</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>2219</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="37.5">
@@ -27300,7 +27755,7 @@
         <v>1289</v>
       </c>
       <c r="C236" s="17" t="s">
-        <v>2220</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -27311,7 +27766,7 @@
         <v>1290</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>2221</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -27322,7 +27777,7 @@
         <v>1291</v>
       </c>
       <c r="C238" s="11" t="s">
-        <v>2222</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -27333,7 +27788,7 @@
         <v>1292</v>
       </c>
       <c r="C239" s="11" t="s">
-        <v>2200</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -27344,7 +27799,7 @@
         <v>1293</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>2223</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -27355,7 +27810,7 @@
         <v>1294</v>
       </c>
       <c r="C241" s="11" t="s">
-        <v>2224</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -27366,7 +27821,7 @@
         <v>1295</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>2225</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="37.5">
@@ -27377,7 +27832,7 @@
         <v>1296</v>
       </c>
       <c r="C243" s="17" t="s">
-        <v>2226</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -27388,7 +27843,7 @@
         <v>1297</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>2227</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -27399,7 +27854,7 @@
         <v>1298</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>2228</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -27410,7 +27865,7 @@
         <v>1299</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>2231</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -27421,7 +27876,7 @@
         <v>1300</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>2232</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -27432,7 +27887,7 @@
         <v>1301</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>2233</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -27443,7 +27898,7 @@
         <v>1302</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>2234</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -27454,7 +27909,7 @@
         <v>1303</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>2235</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="37.5">
@@ -27465,7 +27920,7 @@
         <v>1304</v>
       </c>
       <c r="C251" s="17" t="s">
-        <v>2237</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -27487,7 +27942,7 @@
         <v>1306</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>2239</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -27498,7 +27953,7 @@
         <v>1307</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -27509,7 +27964,7 @@
         <v>1308</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>2240</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -27520,7 +27975,7 @@
         <v>1309</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>2241</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -27531,7 +27986,7 @@
         <v>1310</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>2242</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -27542,7 +27997,7 @@
         <v>1311</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>2243</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="37.5">
@@ -27553,7 +28008,7 @@
         <v>1312</v>
       </c>
       <c r="C259" s="17" t="s">
-        <v>2244</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -27564,7 +28019,7 @@
         <v>1313</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>2245</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -27575,7 +28030,7 @@
         <v>1314</v>
       </c>
       <c r="C261" s="11" t="s">
-        <v>2246</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -27586,7 +28041,7 @@
         <v>1315</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>2247</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -27608,7 +28063,7 @@
         <v>1317</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>2248</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -27619,7 +28074,7 @@
         <v>1318</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>2249</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -27630,7 +28085,7 @@
         <v>1319</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>2250</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -27641,7 +28096,7 @@
         <v>1320</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>2247</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -27652,7 +28107,7 @@
         <v>1321</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>2251</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -27663,7 +28118,7 @@
         <v>1322</v>
       </c>
       <c r="C269" s="11" t="s">
-        <v>2252</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -27674,7 +28129,7 @@
         <v>1323</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>2253</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -27685,7 +28140,7 @@
         <v>1324</v>
       </c>
       <c r="C271" s="11" t="s">
-        <v>2254</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -27696,7 +28151,7 @@
         <v>1325</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>2255</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -27707,7 +28162,7 @@
         <v>1326</v>
       </c>
       <c r="C273" s="11" t="s">
-        <v>2256</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -27718,7 +28173,7 @@
         <v>1327</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>2257</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -27729,7 +28184,7 @@
         <v>1328</v>
       </c>
       <c r="C275" s="11" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -27740,7 +28195,7 @@
         <v>1329</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>2258</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -27751,7 +28206,7 @@
         <v>1330</v>
       </c>
       <c r="C277" s="11" t="s">
-        <v>2259</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -27762,7 +28217,7 @@
         <v>1331</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>2260</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -27773,7 +28228,7 @@
         <v>1332</v>
       </c>
       <c r="C279" s="11" t="s">
-        <v>2261</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="37.5">
@@ -27784,7 +28239,7 @@
         <v>1333</v>
       </c>
       <c r="C280" s="17" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="37.5">
@@ -27795,7 +28250,7 @@
         <v>1334</v>
       </c>
       <c r="C281" s="17" t="s">
-        <v>2263</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -27806,7 +28261,7 @@
         <v>1335</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -27817,7 +28272,7 @@
         <v>1336</v>
       </c>
       <c r="C283" s="11" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="37.5">
@@ -27828,7 +28283,7 @@
         <v>1337</v>
       </c>
       <c r="C284" s="17" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -27839,7 +28294,7 @@
         <v>1338</v>
       </c>
       <c r="C285" s="11" t="s">
-        <v>2267</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -27850,7 +28305,7 @@
         <v>1339</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>2268</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -27861,7 +28316,7 @@
         <v>1340</v>
       </c>
       <c r="C287" s="11" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -27872,7 +28327,7 @@
         <v>1341</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>2270</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -27883,7 +28338,7 @@
         <v>1342</v>
       </c>
       <c r="C289" s="11" t="s">
-        <v>2271</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -27905,7 +28360,7 @@
         <v>1344</v>
       </c>
       <c r="C291" s="17" t="s">
-        <v>2272</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="37.5">
@@ -27916,7 +28371,7 @@
         <v>1345</v>
       </c>
       <c r="C292" s="17" t="s">
-        <v>2273</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="56.25">
@@ -27927,7 +28382,7 @@
         <v>1346</v>
       </c>
       <c r="C293" s="17" t="s">
-        <v>2274</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -27938,7 +28393,7 @@
         <v>1347</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>2276</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -27949,7 +28404,7 @@
         <v>1348</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>2281</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -27960,7 +28415,7 @@
         <v>1349</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -27982,7 +28437,7 @@
         <v>1351</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>2283</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -27993,7 +28448,7 @@
         <v>1352</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>2284</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -28004,7 +28459,7 @@
         <v>1353</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -28015,7 +28470,7 @@
         <v>1354</v>
       </c>
       <c r="C301" s="11" t="s">
-        <v>2285</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -28026,7 +28481,7 @@
         <v>1355</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>2286</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -28037,7 +28492,7 @@
         <v>1356</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>2287</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -28059,7 +28514,7 @@
         <v>1358</v>
       </c>
       <c r="C305" s="11" t="s">
-        <v>2288</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -28070,7 +28525,7 @@
         <v>1359</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -28092,7 +28547,7 @@
         <v>1361</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>2289</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -28103,7 +28558,7 @@
         <v>1362</v>
       </c>
       <c r="C309" s="11" t="s">
-        <v>2290</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="37.5">
@@ -28114,7 +28569,7 @@
         <v>1363</v>
       </c>
       <c r="C310" s="17" t="s">
-        <v>2291</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="37.5">
@@ -28125,7 +28580,7 @@
         <v>1364</v>
       </c>
       <c r="C311" s="17" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="37.5">
@@ -28136,7 +28591,7 @@
         <v>1365</v>
       </c>
       <c r="C312" s="17" t="s">
-        <v>2293</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="37.5">
@@ -28147,7 +28602,7 @@
         <v>1366</v>
       </c>
       <c r="C313" s="17" t="s">
-        <v>2294</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="37.5">
@@ -28158,7 +28613,7 @@
         <v>1367</v>
       </c>
       <c r="C314" s="17" t="s">
-        <v>2295</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -28169,7 +28624,7 @@
         <v>1368</v>
       </c>
       <c r="C315" s="11" t="s">
-        <v>2296</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="37.5">
@@ -28180,7 +28635,7 @@
         <v>1369</v>
       </c>
       <c r="C316" s="17" t="s">
-        <v>2297</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -28191,7 +28646,7 @@
         <v>1370</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>2298</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -28202,7 +28657,7 @@
         <v>1371</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>2299</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="37.5">
@@ -28213,7 +28668,7 @@
         <v>1372</v>
       </c>
       <c r="C319" s="17" t="s">
-        <v>2300</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -28224,7 +28679,7 @@
         <v>1373</v>
       </c>
       <c r="C320" s="11" t="s">
-        <v>2301</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="37.5">
@@ -28235,7 +28690,7 @@
         <v>1374</v>
       </c>
       <c r="C321" s="17" t="s">
-        <v>2302</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -28246,7 +28701,7 @@
         <v>1375</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>2303</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -28257,7 +28712,7 @@
         <v>1376</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>2304</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -28268,7 +28723,7 @@
         <v>1377</v>
       </c>
       <c r="C324" s="11" t="s">
-        <v>2305</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -28279,7 +28734,7 @@
         <v>1378</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>2306</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="37.5">
@@ -28290,7 +28745,7 @@
         <v>1379</v>
       </c>
       <c r="C326" s="17" t="s">
-        <v>2307</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="37.5">
@@ -28301,7 +28756,7 @@
         <v>1380</v>
       </c>
       <c r="C327" s="17" t="s">
-        <v>2308</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -28312,7 +28767,7 @@
         <v>1381</v>
       </c>
       <c r="C328" s="11" t="s">
-        <v>2310</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -28323,7 +28778,7 @@
         <v>1382</v>
       </c>
       <c r="C329" s="11" t="s">
-        <v>2311</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -28334,7 +28789,7 @@
         <v>1383</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>2312</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -28345,7 +28800,7 @@
         <v>1384</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>2313</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -28356,7 +28811,7 @@
         <v>1385</v>
       </c>
       <c r="C332" s="11" t="s">
-        <v>2314</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="37.5">
@@ -28367,7 +28822,7 @@
         <v>1386</v>
       </c>
       <c r="C333" s="17" t="s">
-        <v>2315</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="56.25">
@@ -28378,7 +28833,7 @@
         <v>1387</v>
       </c>
       <c r="C334" s="17" t="s">
-        <v>2316</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="37.5">
@@ -28389,7 +28844,7 @@
         <v>1388</v>
       </c>
       <c r="C335" s="17" t="s">
-        <v>2323</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="37.5">
@@ -28400,7 +28855,7 @@
         <v>1389</v>
       </c>
       <c r="C336" s="17" t="s">
-        <v>2317</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="37.5">
@@ -28411,7 +28866,7 @@
         <v>1390</v>
       </c>
       <c r="C337" s="17" t="s">
-        <v>2318</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -28422,7 +28877,7 @@
         <v>1391</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>2319</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="37.5">
@@ -28433,7 +28888,7 @@
         <v>1392</v>
       </c>
       <c r="C339" s="17" t="s">
-        <v>2320</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -28455,7 +28910,7 @@
         <v>1393</v>
       </c>
       <c r="C341" s="17" t="s">
-        <v>2322</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -28508,7 +28963,7 @@
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="238.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="244.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -28552,7 +29007,7 @@
         <v>1398</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>2324</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -28563,7 +29018,7 @@
         <v>1399</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>2325</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -28574,7 +29029,7 @@
         <v>1400</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>2326</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -28585,7 +29040,7 @@
         <v>1401</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>2327</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -28596,7 +29051,7 @@
         <v>1402</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>2328</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -28607,7 +29062,7 @@
         <v>1403</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>2329</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -28629,7 +29084,7 @@
         <v>1405</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>2330</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -28640,7 +29095,7 @@
         <v>1406</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>2331</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -28651,7 +29106,7 @@
         <v>1407</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -28662,7 +29117,7 @@
         <v>1408</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>2345</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -28673,7 +29128,7 @@
         <v>1409</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>2333</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -28684,7 +29139,7 @@
         <v>1410</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>2334</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5">
@@ -28695,7 +29150,7 @@
         <v>1411</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>2335</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -28706,7 +29161,7 @@
         <v>1412</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>2336</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -28717,7 +29172,7 @@
         <v>1413</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>2337</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -28728,7 +29183,7 @@
         <v>1414</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>2338</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -28739,7 +29194,7 @@
         <v>1415</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>2339</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -28750,7 +29205,7 @@
         <v>1416</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>2340</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -28761,7 +29216,7 @@
         <v>1417</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>2341</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="37.5">
@@ -28772,7 +29227,7 @@
         <v>1418</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>2342</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -28783,7 +29238,7 @@
         <v>1419</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>2343</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -28794,7 +29249,7 @@
         <v>1420</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>2344</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -28816,7 +29271,7 @@
         <v>1422</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>2346</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -28827,7 +29282,7 @@
         <v>1423</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>2347</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -28849,7 +29304,7 @@
         <v>1425</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>2349</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -28860,7 +29315,7 @@
         <v>1426</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>2348</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -28871,7 +29326,7 @@
         <v>1427</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>2350</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -28882,7 +29337,7 @@
         <v>1428</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>2351</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="37.5">
@@ -28893,7 +29348,7 @@
         <v>1429</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>2352</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="37.5">
@@ -28904,7 +29359,7 @@
         <v>1430</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>2353</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="37.5">
@@ -28915,7 +29370,7 @@
         <v>1431</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>2354</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="37.5">
@@ -28926,7 +29381,7 @@
         <v>1432</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>2355</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -28937,7 +29392,7 @@
         <v>1433</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>2356</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -28948,7 +29403,7 @@
         <v>1434</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>2357</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="56.25">
@@ -28959,7 +29414,7 @@
         <v>1435</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>2358</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -28981,7 +29436,7 @@
         <v>1437</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>2413</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -29003,7 +29458,7 @@
         <v>1439</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>2359</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -29014,7 +29469,7 @@
         <v>1440</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>2360</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -29036,7 +29491,7 @@
         <v>1442</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>2361</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="37.5">
@@ -29047,7 +29502,7 @@
         <v>1443</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>2362</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -29058,7 +29513,7 @@
         <v>1444</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>2363</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -29069,7 +29524,7 @@
         <v>1445</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -29080,7 +29535,7 @@
         <v>1446</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>2365</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="56.25">
@@ -29091,7 +29546,7 @@
         <v>1447</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>2366</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -29102,7 +29557,7 @@
         <v>1448</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>2367</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="56.25">
@@ -29113,7 +29568,7 @@
         <v>1449</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>2368</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -29124,7 +29579,7 @@
         <v>1450</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>2369</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="75">
@@ -29135,7 +29590,7 @@
         <v>1451</v>
       </c>
       <c r="C57" s="25" t="s">
-        <v>2370</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -29157,7 +29612,7 @@
         <v>1453</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>2371</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -29179,7 +29634,7 @@
         <v>1455</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>2372</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -29190,7 +29645,7 @@
         <v>1456</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>2378</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -29201,7 +29656,7 @@
         <v>1457</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>2373</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -29212,7 +29667,7 @@
         <v>1458</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>2374</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -29234,7 +29689,7 @@
         <v>1460</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>2375</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -29245,7 +29700,7 @@
         <v>1461</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>2376</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -29256,7 +29711,7 @@
         <v>1462</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>2377</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -29267,7 +29722,7 @@
         <v>1463</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>2379</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -29278,7 +29733,7 @@
         <v>1464</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>2380</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="56.25">
@@ -29289,7 +29744,7 @@
         <v>1465</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>2381</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -29300,7 +29755,7 @@
         <v>1466</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>2382</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -29311,7 +29766,7 @@
         <v>1467</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>2383</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="56.25">
@@ -29322,7 +29777,7 @@
         <v>1468</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>2384</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -29355,7 +29810,7 @@
         <v>1471</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>2385</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -29366,7 +29821,7 @@
         <v>1472</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>2386</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="37.5">
@@ -29377,7 +29832,7 @@
         <v>1473</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>2387</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -29388,7 +29843,7 @@
         <v>1474</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>2388</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="37.5">
@@ -29399,7 +29854,7 @@
         <v>1475</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>2389</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -29410,7 +29865,7 @@
         <v>1476</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>2390</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -29432,7 +29887,7 @@
         <v>1478</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>2393</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="37.5">
@@ -29443,7 +29898,7 @@
         <v>1479</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>2394</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -29454,7 +29909,7 @@
         <v>1480</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>2395</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -29465,7 +29920,7 @@
         <v>1481</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>2396</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="56.25">
@@ -29476,7 +29931,7 @@
         <v>1482</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>2397</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="56.25">
@@ -29487,7 +29942,7 @@
         <v>1483</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>2398</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="37.5">
@@ -29498,7 +29953,7 @@
         <v>1484</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>2401</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="37.5">
@@ -29509,7 +29964,7 @@
         <v>1485</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>2402</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="37.5">
@@ -29520,7 +29975,7 @@
         <v>1486</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>2403</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -29542,7 +29997,7 @@
         <v>1488</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>2404</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -29553,7 +30008,7 @@
         <v>1489</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>2405</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -29564,7 +30019,7 @@
         <v>1490</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>2406</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -29575,7 +30030,7 @@
         <v>1491</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>2407</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -29586,7 +30041,7 @@
         <v>1492</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>2408</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -29597,7 +30052,7 @@
         <v>1493</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>2409</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -29608,7 +30063,7 @@
         <v>1494</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>2410</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -29619,7 +30074,7 @@
         <v>1495</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>2411</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -29630,7 +30085,7 @@
         <v>1496</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>2412</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -29641,7 +30096,7 @@
         <v>1497</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>2414</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="37.5">
@@ -29652,7 +30107,7 @@
         <v>1498</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>2415</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -29663,7 +30118,7 @@
         <v>1499</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>2416</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -29674,7 +30129,7 @@
         <v>1500</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>2417</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -29685,7 +30140,7 @@
         <v>1501</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>2418</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -29696,7 +30151,7 @@
         <v>1502</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>2419</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -29707,7 +30162,7 @@
         <v>1503</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>2420</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -29718,7 +30173,7 @@
         <v>1504</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -29729,7 +30184,7 @@
         <v>1505</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>2285</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -29740,7 +30195,7 @@
         <v>1506</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>2422</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="56.25">
@@ -29751,7 +30206,7 @@
         <v>1507</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>2423</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -29762,7 +30217,7 @@
         <v>1508</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>2424</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -29773,7 +30228,7 @@
         <v>1509</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>2425</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="37.5">
@@ -29784,7 +30239,7 @@
         <v>1510</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>2426</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="37.5">
@@ -29795,7 +30250,7 @@
         <v>1511</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>2427</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -29806,7 +30261,7 @@
         <v>1512</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>2428</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -29817,7 +30272,7 @@
         <v>1513</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>2429</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -29828,7 +30283,7 @@
         <v>1514</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>2430</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="37.5">
@@ -29839,7 +30294,7 @@
         <v>1515</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>2431</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -29850,7 +30305,7 @@
         <v>1516</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>2432</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="37.5">
@@ -29861,7 +30316,7 @@
         <v>1517</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>2433</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="37.5">
@@ -29872,7 +30327,7 @@
         <v>1518</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>2436</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="37.5">
@@ -29883,7 +30338,7 @@
         <v>1519</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>2437</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="37.5">
@@ -29894,7 +30349,7 @@
         <v>1520</v>
       </c>
       <c r="C126" s="26" t="s">
-        <v>2438</v>
+        <v>2421</v>
       </c>
     </row>
   </sheetData>
@@ -29936,7 +30391,7 @@
         <v>1521</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>2439</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -29947,7 +30402,7 @@
         <v>1522</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>2440</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -29958,7 +30413,7 @@
         <v>1523</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>2467</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -29969,7 +30424,7 @@
         <v>1524</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>2441</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -29980,7 +30435,7 @@
         <v>1525</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>2442</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -29991,7 +30446,7 @@
         <v>1526</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>2443</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -30002,7 +30457,7 @@
         <v>1527</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>2444</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -30013,7 +30468,7 @@
         <v>1528</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>2445</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="37.5">
@@ -30024,7 +30479,7 @@
         <v>1529</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>2446</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -30035,7 +30490,7 @@
         <v>1530</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>2485</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -30046,7 +30501,7 @@
         <v>1531</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>2447</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -30057,7 +30512,7 @@
         <v>1532</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>2448</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -30068,7 +30523,7 @@
         <v>1533</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>2449</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="37.5">
@@ -30079,7 +30534,7 @@
         <v>1534</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>2450</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -30090,7 +30545,7 @@
         <v>1535</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>2451</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -30101,7 +30556,7 @@
         <v>1536</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>2452</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -30112,7 +30567,7 @@
         <v>1537</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>2453</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37.5">
@@ -30123,7 +30578,7 @@
         <v>1538</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>2454</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="37.5">
@@ -30134,7 +30589,7 @@
         <v>1539</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>2455</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="37.5">
@@ -30145,7 +30600,7 @@
         <v>1540</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>2465</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -30156,7 +30611,7 @@
         <v>1541</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>2456</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="37.5">
@@ -30167,7 +30622,7 @@
         <v>1542</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>2457</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -30178,7 +30633,7 @@
         <v>1543</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>2458</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -30189,7 +30644,7 @@
         <v>1544</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>2459</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -30200,7 +30655,7 @@
         <v>1545</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>2460</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="37.5">
@@ -30211,7 +30666,7 @@
         <v>1546</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>2461</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="37.5">
@@ -30222,7 +30677,7 @@
         <v>1547</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>2462</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="93.75">
@@ -30233,7 +30688,7 @@
         <v>1548</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>2466</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -30255,7 +30710,7 @@
         <v>1550</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>2468</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -30277,7 +30732,7 @@
         <v>1552</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>2469</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -30288,7 +30743,7 @@
         <v>1553</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>2470</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="37.5">
@@ -30299,7 +30754,7 @@
         <v>1554</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>2471</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -30310,7 +30765,7 @@
         <v>1555</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>2472</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="37.5">
@@ -30321,7 +30776,7 @@
         <v>1556</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>2473</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -30343,7 +30798,7 @@
         <v>1558</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>2474</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -30354,7 +30809,7 @@
         <v>1559</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>2475</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="56.25">
@@ -30365,7 +30820,7 @@
         <v>1560</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>2476</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="56.25">
@@ -30376,7 +30831,7 @@
         <v>1561</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>2477</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="37.5">
@@ -30387,7 +30842,7 @@
         <v>1562</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>2478</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -30398,7 +30853,7 @@
         <v>1563</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>2480</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -30409,7 +30864,7 @@
         <v>1564</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>2481</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -30431,7 +30886,7 @@
         <v>1566</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>2482</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="37.5">
@@ -30442,7 +30897,7 @@
         <v>1567</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>2483</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="37.5">
@@ -30453,7 +30908,7 @@
         <v>1568</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>2484</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -30464,7 +30919,7 @@
         <v>1569</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>2486</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -30475,7 +30930,7 @@
         <v>1570</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>2487</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="37.5">
@@ -30486,7 +30941,7 @@
         <v>1571</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>2488</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="37.5">
@@ -30497,7 +30952,7 @@
         <v>1572</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>2489</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="37.5">
@@ -30508,7 +30963,7 @@
         <v>1573</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>2490</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="37.5">
@@ -30519,7 +30974,7 @@
         <v>1574</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>2491</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="37.5">
@@ -30530,7 +30985,7 @@
         <v>1575</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -30541,7 +30996,7 @@
         <v>1576</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>1576</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -30552,7 +31007,7 @@
         <v>1577</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>1577</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -30563,7 +31018,7 @@
         <v>1578</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>1578</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -30574,7 +31029,7 @@
         <v>1579</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>1579</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -30585,40 +31040,40 @@
         <v>1580</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="37.5">
       <c r="A62" s="12">
         <v>103405</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>1581</v>
       </c>
-      <c r="C62" s="19" t="s">
-        <v>1581</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="C62" s="25" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="37.5">
       <c r="A63" s="12">
         <v>103406</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>1582</v>
       </c>
-      <c r="C63" s="19" t="s">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="C63" s="25" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="37.5">
       <c r="A64" s="12">
         <v>103407</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>1583</v>
       </c>
-      <c r="C64" s="19" t="s">
-        <v>1583</v>
+      <c r="C64" s="25" t="s">
+        <v>2483</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -30629,7 +31084,7 @@
         <v>1584</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>1584</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -30640,29 +31095,29 @@
         <v>1585</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>1585</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="37.5">
       <c r="A67" s="12">
         <v>103410</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>1586</v>
       </c>
-      <c r="C67" s="19" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="C67" s="25" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="37.5">
       <c r="A68" s="12">
         <v>103411</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>1587</v>
       </c>
-      <c r="C68" s="19" t="s">
-        <v>1587</v>
+      <c r="C68" s="25" t="s">
+        <v>2487</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -30673,40 +31128,40 @@
         <v>1588</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="37.5">
       <c r="A70" s="12">
         <v>103500</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>1589</v>
       </c>
-      <c r="C70" s="19" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="C70" s="25" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="37.5">
       <c r="A71" s="12">
         <v>103501</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>1590</v>
       </c>
-      <c r="C71" s="19" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="C71" s="25" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="37.5">
       <c r="A72" s="12">
         <v>103502</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>1591</v>
       </c>
-      <c r="C72" s="19" t="s">
-        <v>1591</v>
+      <c r="C72" s="25" t="s">
+        <v>2491</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -30717,29 +31172,29 @@
         <v>1592</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>1592</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="37.5">
       <c r="A74" s="12">
         <v>103504</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>1593</v>
       </c>
-      <c r="C74" s="19" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="C74" s="25" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="37.5">
       <c r="A75" s="12">
         <v>103505</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>1594</v>
       </c>
-      <c r="C75" s="19" t="s">
-        <v>1594</v>
+      <c r="C75" s="25" t="s">
+        <v>2494</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -30750,18 +31205,18 @@
         <v>1595</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="37.5">
       <c r="A77" s="12">
         <v>103507</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>1596</v>
       </c>
-      <c r="C77" s="19" t="s">
-        <v>1596</v>
+      <c r="C77" s="25" t="s">
+        <v>2496</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -30772,40 +31227,40 @@
         <v>1597</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="37.5">
       <c r="A79" s="12">
         <v>103509</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>1598</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>1598</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="C79" s="25" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="37.5">
       <c r="A80" s="12">
         <v>103510</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>1599</v>
       </c>
-      <c r="C80" s="19" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="C80" s="25" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="37.5">
       <c r="A81" s="12">
         <v>103511</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>1600</v>
       </c>
-      <c r="C81" s="19" t="s">
-        <v>1600</v>
+      <c r="C81" s="25" t="s">
+        <v>2501</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -30816,7 +31271,7 @@
         <v>1601</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>1601</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -30827,18 +31282,18 @@
         <v>1602</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="37.5">
       <c r="A84" s="12">
         <v>103601</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>1603</v>
       </c>
-      <c r="C84" s="19" t="s">
-        <v>1603</v>
+      <c r="C84" s="25" t="s">
+        <v>2503</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -30849,7 +31304,7 @@
         <v>1604</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>1604</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -30860,40 +31315,40 @@
         <v>1605</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="37.5">
       <c r="A87" s="12">
         <v>103604</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>1606</v>
       </c>
-      <c r="C87" s="19" t="s">
-        <v>1606</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="C87" s="25" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="37.5">
       <c r="A88" s="12">
         <v>103605</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>1607</v>
       </c>
-      <c r="C88" s="19" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="C88" s="25" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="37.5">
       <c r="A89" s="12">
         <v>103606</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>1608</v>
       </c>
-      <c r="C89" s="19" t="s">
-        <v>1608</v>
+      <c r="C89" s="25" t="s">
+        <v>2508</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -30904,7 +31359,7 @@
         <v>1609</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>1609</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -30915,51 +31370,51 @@
         <v>1610</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="37.5">
       <c r="A92" s="12">
         <v>103609</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>1611</v>
       </c>
-      <c r="C92" s="19" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="C92" s="25" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="37.5">
       <c r="A93" s="12">
         <v>103610</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>1612</v>
       </c>
-      <c r="C93" s="19" t="s">
-        <v>1612</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="C93" s="25" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="37.5">
       <c r="A94" s="12">
         <v>103611</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>1613</v>
       </c>
-      <c r="C94" s="19" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="C94" s="25" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="37.5">
       <c r="A95" s="12">
         <v>103612</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>1614</v>
       </c>
-      <c r="C95" s="19" t="s">
-        <v>1614</v>
+      <c r="C95" s="25" t="s">
+        <v>2514</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -30970,7 +31425,7 @@
         <v>1615</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>1615</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -30981,7 +31436,7 @@
         <v>1616</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>1616</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -30992,7 +31447,7 @@
         <v>1617</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>1617</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -31003,7 +31458,7 @@
         <v>1618</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>1618</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -31014,18 +31469,18 @@
         <v>1619</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="37.5">
       <c r="A101" s="12">
         <v>103705</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>1620</v>
       </c>
-      <c r="C101" s="19" t="s">
-        <v>1620</v>
+      <c r="C101" s="25" t="s">
+        <v>2523</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -31036,7 +31491,7 @@
         <v>1621</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>1621</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -31047,18 +31502,18 @@
         <v>1622</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="37.5">
       <c r="A104" s="12">
         <v>103708</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>1623</v>
       </c>
-      <c r="C104" s="19" t="s">
-        <v>1623</v>
+      <c r="C104" s="25" t="s">
+        <v>2544</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -31069,40 +31524,40 @@
         <v>1624</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="37.5">
       <c r="A106" s="12">
         <v>103710</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>1625</v>
       </c>
-      <c r="C106" s="19" t="s">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="C106" s="25" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="56.25">
       <c r="A107" s="12">
         <v>103711</v>
       </c>
       <c r="B107" s="11" t="s">
         <v>1626</v>
       </c>
-      <c r="C107" s="19" t="s">
-        <v>1626</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="C107" s="25" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="75">
       <c r="A108" s="15">
         <v>103712</v>
       </c>
       <c r="B108" s="16" t="s">
         <v>1627</v>
       </c>
-      <c r="C108" s="20" t="s">
-        <v>1627</v>
+      <c r="C108" s="26" t="s">
+        <v>2548</v>
       </c>
     </row>
     <row r="109" spans="1:3">

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DBDAD4-EC56-4921-AA12-9FA413B77431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE553F7-5410-4665-8A5E-7452170534E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="InfinityEvolved" sheetId="44" r:id="rId3"/>
     <sheet name="HeirsOfTheOmen" sheetId="45" r:id="rId4"/>
     <sheet name="SkyboundDragons" sheetId="46" r:id="rId5"/>
-    <sheet name="Basic" sheetId="47" r:id="rId6"/>
-    <sheet name="CLC" sheetId="48" r:id="rId7"/>
-    <sheet name="DRK" sheetId="49" r:id="rId8"/>
-    <sheet name="ROB" sheetId="50" r:id="rId9"/>
-    <sheet name="TOG" sheetId="51" r:id="rId10"/>
-    <sheet name="WLD" sheetId="52" r:id="rId11"/>
-    <sheet name="Select" sheetId="81" r:id="rId12"/>
-    <sheet name="memo" sheetId="82" r:id="rId13"/>
+    <sheet name="BlossomingFate" sheetId="83" r:id="rId6"/>
+    <sheet name="Basic" sheetId="47" r:id="rId7"/>
+    <sheet name="CLC" sheetId="48" r:id="rId8"/>
+    <sheet name="DRK" sheetId="49" r:id="rId9"/>
+    <sheet name="ROB" sheetId="50" r:id="rId10"/>
+    <sheet name="TOG" sheetId="51" r:id="rId11"/>
+    <sheet name="WLD" sheetId="52" r:id="rId12"/>
+    <sheet name="Select" sheetId="81" r:id="rId13"/>
+    <sheet name="memo" sheetId="82" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="2761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3089" uniqueCount="2915">
   <si>
     <t>フェアリー</t>
     <phoneticPr fontId="1"/>
@@ -15618,6 +15619,653 @@
     <rPh sb="90" eb="92">
       <t>ハカイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>達筆の怪異</t>
+  </si>
+  <si>
+    <t>軍配の偉丈夫</t>
+  </si>
+  <si>
+    <t>スターライトゴッデス</t>
+  </si>
+  <si>
+    <t>《世界》の提示</t>
+  </si>
+  <si>
+    <t>大遊戯世界</t>
+  </si>
+  <si>
+    <t>八界花・ゲテンオウ</t>
+  </si>
+  <si>
+    <t>賢慮の狸</t>
+  </si>
+  <si>
+    <t>森羽子板の匠</t>
+  </si>
+  <si>
+    <t>虫風花の飛翔</t>
+  </si>
+  <si>
+    <t>バディングバディーズ</t>
+  </si>
+  <si>
+    <t>和気藹々の妖精</t>
+  </si>
+  <si>
+    <t>静かなる応援</t>
+  </si>
+  <si>
+    <t>導きの船頭</t>
+  </si>
+  <si>
+    <t>優雅なる虫風花</t>
+  </si>
+  <si>
+    <t>天踏む《吊るされた男》・ローフラッド</t>
+  </si>
+  <si>
+    <t>虫風花・ミロク</t>
+  </si>
+  <si>
+    <t>煙管の美玉</t>
+  </si>
+  <si>
+    <t>喜捨の名士</t>
+  </si>
+  <si>
+    <t>麗金花の散財</t>
+  </si>
+  <si>
+    <t>剽疾の武闘家</t>
+  </si>
+  <si>
+    <t>吉祥蛙</t>
+  </si>
+  <si>
+    <t>優しき援軍</t>
+  </si>
+  <si>
+    <t>不動の将校</t>
+  </si>
+  <si>
+    <t>栄耀なる麗金花</t>
+  </si>
+  <si>
+    <t>麗金花・ウンケイ</t>
+  </si>
+  <si>
+    <t>猛る《戦車》・オルオーン</t>
+  </si>
+  <si>
+    <t>輝く金貨</t>
+  </si>
+  <si>
+    <t>シェイプウィザード</t>
+  </si>
+  <si>
+    <t>流動の符操師</t>
+  </si>
+  <si>
+    <t>明越花の転変</t>
+  </si>
+  <si>
+    <t>インソムニアウィッチ</t>
+  </si>
+  <si>
+    <t>余情の俳人</t>
+  </si>
+  <si>
+    <t>キティトリック</t>
+  </si>
+  <si>
+    <t>エレメンタルガバナー</t>
+  </si>
+  <si>
+    <t>壮美なる明越花</t>
+  </si>
+  <si>
+    <t>歩む《愚者》・リンクル</t>
+  </si>
+  <si>
+    <t>明越花・アラ</t>
+  </si>
+  <si>
+    <t>湧水の汲み手</t>
+  </si>
+  <si>
+    <t>雫の囃子方</t>
+  </si>
+  <si>
+    <t>波揺花の断裁</t>
+  </si>
+  <si>
+    <t>クラゲの舞姫</t>
+  </si>
+  <si>
+    <t>鉄槌のドラグーン</t>
+  </si>
+  <si>
+    <t>プロミネンスロア</t>
+  </si>
+  <si>
+    <t>ルインジェノサイダー</t>
+  </si>
+  <si>
+    <t>怠惰なる波揺花</t>
+  </si>
+  <si>
+    <t>波揺花・ユウベ</t>
+  </si>
+  <si>
+    <t>律する《正義》・イランツァ</t>
+  </si>
+  <si>
+    <t>リリーブウルフ</t>
+  </si>
+  <si>
+    <t>紅札の魂魄使い</t>
+  </si>
+  <si>
+    <t>奥夜花の開戦</t>
+  </si>
+  <si>
+    <t>トラブルネクロマンサー</t>
+  </si>
+  <si>
+    <t>橋渡しの青鬼</t>
+  </si>
+  <si>
+    <t>残虐の炸裂</t>
+  </si>
+  <si>
+    <t>フェイタルテイカー</t>
+  </si>
+  <si>
+    <t>厳酷なる奥夜花</t>
+  </si>
+  <si>
+    <t>充つ《恋人と節制》・ミルティオ＆ルーゼン</t>
+  </si>
+  <si>
+    <t>奥夜花・シャクドウ</t>
+  </si>
+  <si>
+    <t>結びの使徒</t>
+  </si>
+  <si>
+    <t>フォアサイトプリースト</t>
+  </si>
+  <si>
+    <t>霧巻花の激憤</t>
+  </si>
+  <si>
+    <t>窮鼠の斎女</t>
+  </si>
+  <si>
+    <t>イムーバブルパラディン</t>
+  </si>
+  <si>
+    <t>プロテクションシェル</t>
+  </si>
+  <si>
+    <t>威徳の至聖</t>
+  </si>
+  <si>
+    <t>堅固なる霧巻花</t>
+  </si>
+  <si>
+    <t>想う《力》・ソフィーナ</t>
+  </si>
+  <si>
+    <t>霧巻花・クキシロ</t>
+  </si>
+  <si>
+    <t>ステージメーカー</t>
+  </si>
+  <si>
+    <t>満開の技術屋</t>
+  </si>
+  <si>
+    <t>尽小花の照臨</t>
+  </si>
+  <si>
+    <t>清宵の偶兎</t>
+  </si>
+  <si>
+    <t>ネオジオグラファー</t>
+  </si>
+  <si>
+    <t>リヴァイブチューニング</t>
+  </si>
+  <si>
+    <t>ニューロンインタラプター</t>
+  </si>
+  <si>
+    <t>誠心なる尽小花</t>
+  </si>
+  <si>
+    <t>尽小花・イマリ</t>
+  </si>
+  <si>
+    <t>廻る《運命の輪》・スロース</t>
+  </si>
+  <si>
+    <t>イマリの小鬼</t>
+  </si>
+  <si>
+    <t>【ファンファーレ】場に他の元のコスト1のカードがあるなら、これは+1/+1する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】自分の手札の元のコストの大きい順に3枚の合計が相手の手札の元のコストの大きい順に3枚の合計より大きいなら、相手の場のフォロワーすべてを破壊。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】自分の手札3枚を選ぶ。それを捨てる。自分の手札左から3枚のコピー1枚ずつを非公開で自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のデッキから2枚を引く。相手の場の攻撃力最大のフォロワーからランダム1枚を破壊。
+【エンハンス_10】相手の場のフォロワーすべてと相手のリーダーに4ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【カウントダウン_5】
+自分が他のカードをプレイしたとき、場にそれ以外の元のコストXのカードがあるなら、これのカウントを-1する。Xはプレイしたカードの元のコストである。
+【ラストワード】自分のデッキから2枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札すべてを捨てる。【モード】1つを選んでその能力が働く。
+（1）自分のデッキから8枚を引く。
+（2）自分のデッキから2枚を引く。それのコストを-8する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【潜伏】
+【進化時】自分のデッキから1枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『フェアリー』1枚を自分の場に出す。
+自分の妖精・フォロワーが場に出たとき、相手のリーダーに1ダメージ。
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワーすべてに3ダメージを割りふる。『フェアリー』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【コンボ_5】『バディングバディーズ』1枚を自分の場に出す。それとこれは進化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【突進】
+【必殺】
+【ドレイン】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワーすべてと相手のリーダーに1ダメージ。【コンボ_3】1ダメージではなく2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『フェアリー』3枚を自分の場に出す。
+【進化時】【ファンファーレ】と同じ能力が働く。
+【超進化時】自分の場の妖精・フォロワーすべては【必殺】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のデッキからX枚を引く。Xは自分の【コンボ】である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】これは+X/+Xする。Xは自分の【コンボ】である。
+【進化時】自分の手札すべてを捨てる。相手のデッキからランダム5枚のコピー1枚ずつを非公開で自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【モード】1つを選んでその能力が働く。
+（1）『フェアリー』2枚を自分の手札に加える。
+（2）自分のPPを2回復。
+（3）相手の場のフォロワーすべてに3ダメージを割りふる。
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札のスペルの枚数が2以上なら、これは+1/+1して【守護】を持つ。
+【進化時】『輝く金貨』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札1枚を選ぶ。それを捨てる。自分のリーダーを3回復。スペルを選んだなら、3回復ではなく6回復。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の手札のスペル1枚を選ぶ。それを捨てる。「相手の場のフォロワーからランダム1枚に3ダメージ。」を2回行う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これを引いたとき、ターン終了まで、これのコストを3にする。
+【ファンファーレ】自分のデッキから1枚を引く。自分のリーダーを3回復。
+【突進】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のターン終了時、自分の手札のスペルの枚数が2以上なら、相手の場のフォロワーすべてに5ダメージ。
+【進化時】『輝く金貨』2枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『ナイト』2枚を自分の場に出す。
+【エンハンス_4】2枚ではなく4枚。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォロワーやリーダーを攻撃できない。
+自分のターン終了時、『スティールナイト』1枚を自分の場に出す。
+【超進化時】自分の場の他のフォロワーすべては+3/+3する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>『輝く金貨』2枚を自分の手札に加える。
+【エンハンス_5】2枚ではなく4枚。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それを消滅。『輝く金貨』1枚を自分の手札に加える。
+【超進化時】自分は『クレスト：麗金花・ウンケイ』を持つ。
+クレスト
+【カウントダウン_4】
+自分のターン終了時、『輝く金貨』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のターン終了時、これが進化前なら、相手の場のフォロワーすべてに7ダメージ。進化後なら、「場の他のフォロワーか自分のリーダーか相手のリーダーからランダム1枚に7ダメージ。」を3回行う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【モード】1つを選んでその能力が働く。
+（1）自分のデッキから1枚を引く。
+（2）相手の場のフォロワーからランダム1枚に2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の場の土の印を+2する。
+【超進化時】『ガーディアンゴーレム』2枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワーからランダム3枚に3ダメージ。自分の手札すべては3回スペルブーストする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の手札1枚を選ぶ。それを捨てる。自分のデッキから2枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分は『クレスト：インソムニアウィッチ』を持つ。
+【進化時】自分の『クレスト：インソムニアウィッチ』を破壊。
+クレスト
+【カウントダウン_2】
+【ラストワード】場のフォロワーすべてに3ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【スペルブースト時】これのコストを-1する。
+【ファンファーレ】自分のデッキから1枚を引く。
+【ラストワード】自分の手札すべては1回スペルブーストする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【土の秘術_2】下記の能力からランダム2つの能力が働く。
+（1）『クレイゴーレム』1枚を自分の場に出す。
+（2）自分のリーダーを2回復。
+（3）自分の場の土の印を+3する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『ガーディアンゴーレム』2枚を自分の場に出す。
+自分のゴーレム・フォロワーが場に出たとき、【土の秘術_1】それは進化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の場のフォロワーすべてはそれぞれ、自分のデッキのフォロワーからランダム1枚のコピーに変身する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分は『クレスト：歩む《愚者》・リンクル』を持つ。
+【突進】
+【超進化時】『歩む《愚者》・リンクル』10枚を自分のデッキに加える。
+クレスト
+自分の『歩む《愚者》・リンクル』が場に出たとき、相手のリーダーの体力の最大値を-2する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【スペルブースト時】これのコストを-1する。
+【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それに10ダメージ。
+【進化時】場の他のフォロワー1枚を選ぶ。それは『壮麗なる隼』に変身する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【進化時】相手の場のフォロワー1枚を選ぶ。それに5ダメージ。
+【超進化時】1枚ではなく2枚。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『大海のオルカ』1枚を自分の場に出す。
+自分の海洋・フォロワーが場に出たとき、自分のリーダーを2回復。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分のデッキからフォロワー1枚を引く。相手の場のフォロワーからランダム1枚にXダメージ。Xはこれで引いたカードのコストである。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『大海のオルカ』1枚を自分の手札に加える。
+自分の海洋・フォロワーが場に出たとき、これは【突進】と【必殺】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それに7ダメージ。『大翼のドラゴン』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場のフォロワーすべてにXダメージ。Xは場のフォロワーの枚数である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【超進化時】自分のデッキのコスト1、3、5、7、9のカードすべてを消滅。相手の場のフォロワーすべてにXダメージを割りふる。Xはこれで消滅したカードの枚数である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「相手の場のフォロワーからランダム1枚に2ダメージ。」を2回行う。【覚醒】なら、相手のリーダーに2ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『大海のオルカ』1枚を自分の場に出す。
+【進化時】自分の手札1枚を選ぶ。それを捨てる。自分は『クレスト：波揺花・ユウベ』を持つ。
+クレスト
+自分の海洋・フォロワーが攻撃するとき、ターン終了まで、それは+1/+0する。自分のターンごとに1回、『大海のオルカ』1枚を自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+自分のターン終了時、これが進化前なら、相手の場のフォロワーからランダム2枚に8ダメージ。自分のリーダーを8回復。進化後なら、相手のリーダーに8ダメージ。
+【進化時】これは【守護】を失う。これは【威圧】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_6】これは+0/+6して【必殺】と【バリア】を持つ。
+【突進】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【リアニメイト_2】を行う。
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相手の場のフォロワー1枚を選ぶ。それに5ダメージ。『奥夜花の開戦』1枚を自分のデッキに加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『ゴースト』1枚と『スケルトン』1枚を自分の場に出す。
+【進化時】『腐臭のゾンビ』1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。相手のターン終了まで、それは「フォロワーやリーダーを攻撃できない。」を持つ。自分のデッキから1枚を引く。
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力最小のリーダーすべてに3ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】場の他のフォロワーすべては『スケルトン』に変身する。
+『スケルトン』が破壊されたとき、自分のリーダーを1回復。
+【進化時】場の他のフォロワーすべてに1ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分は『クレスト：厳酷なる奥夜花』を持つ。
+クレスト
+【カウントダウン_2】
+自分のターン終了時、自分のデッキから1枚を引く。その後、自分の手札に4枚以上同じコストがあるなら、『スケルトン』1枚を自分の場に出す。それは【守護】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【リアニメイト_4】と【リアニメイト_2】を行う。
+これが進化したとき、場の他のフォロワーからランダム6枚を破壊。
+これが超進化したとき、自分は『クレスト：充つ《恋人と節制》・ミルティオ＆ルーゼン』を持つ。
+クレスト
+自分のフォロワーの【ファンファーレ】や【エンハンス】は働かない。
+自分がフォロワーをプレイしたとき、それは進化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】「自分の手札すべてをデッキに戻す。自分のデッキからX枚を引く。Xはこれでデッキに戻した枚数である。その後、自分の手札に4枚以上同じコストがあるなら、相手の場のフォロワーすべてと相手のリーダーに4ダメージ。」を2回行う。
+【超進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【エンハンス_4】自分のデッキから1枚を引く。これは【必殺】を持つ。
+自分がカードを引いたとき、自分のターンなら、これは【突進】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それに2ダメージ。
+【守護】
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の手札からランダム1枚をデッキに戻す。自分のデッキから3枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のデッキから1枚を引く。
+自分がカードを引いたとき、自分のターンなら、相手の場のフォロワーすべてに1ダメージ。
+【進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『イムーバブルパラディン』3枚を自分の場に出す。
+【守護】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【アクト】これを破壊。自分のデッキからX枚を引く。Xは自分の場の【守護】を持つフォロワーの枚数である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のリーダーを1回復。
+【守護】
+自分のリーダーが回復したとき、自分のターンなら、『清純なる白狐』1枚を自分の場に出す。
+【進化時】【ファンファーレ】と同じ能力が働く。
+【超進化時】【ファンファーレ】と同じ能力が働く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】相手の場のフォロワー1枚を選ぶ。それに5ダメージ。
+【アクト】これを破壊。自分の手札からランダム2枚をデッキに戻す。自分のデッキから2枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】【モード】1つを選んでその能力が働く。
+（1）これは進化する。
+（2）自分の場の他の「【守護】を持つ、進化前のフォロワー」からランダム1枚は進化する。それは+1/+1する。
+【守護】
+自分のターン終了時、これが進化後なら、場の他のフォロワーすべては-1/-1する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分は『クレスト：霧巻花・クキシロ』を持つ。自分の手札からランダム2枚をデッキに戻す。自分のデッキから2枚を引く。
+【突進】
+クレスト
+自分がコスト1、3、5のカードを引いたとき、自分のターンなら、『清純なる白狐』『ホーリーファルコン』からランダム1枚を自分の場に出す。
+自分がコスト2、4、6のカードを引いたとき、自分のターンなら、『清純なる白狐』『ホーリーファルコン』からランダム1枚を相手の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『改良型・操り人形』1枚と『操り人形』1枚を自分の場に出す。
+【エンハンス_7】それは【疾走】を持つ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のデッキからスペル1枚を引く。
+自分がスペルをプレイしたとき、相手の場のフォロワーすべてに3ダメージ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【守護】
+自分がスペルをプレイしたとき、これは進化する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】『デストロイアーティファクトβ』1枚を自分の手札に加える。
+【超進化時】自分の手札のコスト5以下のアーティファクト・フォロワー1枚を選ぶ。それのコピー1枚を自分の場に出す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分の手札1枚を選ぶ。それを捨てる。このバトル中に破壊された自分のフォロワーからランダム2種類と同名のカード1枚ずつを非公開で自分の手札に加える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分のPPをX回復。Xは自分の場の他のフォロワーの枚数である。
+【突進】
+【ラストワード】自分のデッキから2枚を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場のカード1枚を選ぶ。それは『イマリの小鬼』に変身する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【ファンファーレ】自分の手札1枚を選ぶ。それを捨てる。自分のデッキからスペル1枚を引く。
+自分がスペルをプレイしたとき、これが進化後なら、『イマリの小鬼』1枚を自分の場に出す。
+【超進化時】自分のデッキからコスト1のスペル2種類を引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【潜伏】
+自分のターン終了時、これが進化後なら、相手は『クレスト：廻る《運命の輪》・スロース』を持つ。これを消滅。
+自分のターン開始時、下記の能力から働いていないランダム1つの能力が働く。
+（1）ターン終了まで、自分の手札すべてのコストを-1する。
+（2）自分の場のフォロワーすべては+2/+2する。
+（3）自分のリーダーを3回復。
+クレスト
+【カウントダウン_3】
+自分のターン開始時、下記の能力から働いていないランダム1つの能力が働く。
+（1）ターン終了まで、自分の手札すべてのコストを+1する。
+（2）自分の場のフォロワーすべては-2/-2する。
+（3）自分のリーダーに3ダメージ。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -15808,7 +16456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -15864,38 +16512,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
     <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -15914,37 +16554,15 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -15959,47 +16577,10 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
-          <fgColor indexed="64"/>
+          <fgColor rgb="FF000000"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -16014,94 +16595,6 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -16186,37 +16679,34 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color indexed="64"/>
-        </right>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -16226,13 +16716,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -16292,6 +16775,49 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
         <patternFill patternType="none">
@@ -16345,6 +16871,147 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="177" formatCode="000000"/>
       <fill>
         <patternFill patternType="none">
@@ -16379,6 +17046,51 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -16584,33 +17296,45 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}" name="テーブル1" displayName="テーブル1" ref="A1:C77" totalsRowShown="0">
   <autoFilter ref="A1:C77" xr:uid="{D63B181B-9B76-4271-8A9D-BD1A083B7461}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{D5AF26B8-2D45-4875-94D1-B9BA8F02D74A}" name="ID" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{9D0E108C-09B3-41C6-8FD6-6499B7F88C73}" name="Name" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{8FB8E4A9-49C5-4040-BE02-1D73823BA08B}" name="CardText" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="19" tableBorderDxfId="18" totalsRowBorderDxfId="17">
-  <autoFilter ref="A1:C108" xr:uid="{E15C51F9-F521-433C-8765-752424375382}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+  <autoFilter ref="A1:C108" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:C108" xr:uid="{E15C51F9-F521-433C-8765-752424375382}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:C109" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16620,7 +17344,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}" name="テーブル3" displayName="テーブル3" ref="A1:C166" totalsRowShown="0">
   <autoFilter ref="A1:C166" xr:uid="{CFC6C874-6A37-45C4-91B4-88AB979E3FA9}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{65F48032-C0C0-4AEE-9939-D419BE69326C}" name="ID" dataDxfId="45"/>
     <tableColumn id="2" xr3:uid="{AE50F308-AC9C-41D0-959A-F605A2B1244D}" name="Name"/>
     <tableColumn id="3" xr3:uid="{49ACDFEA-EE20-40A5-A482-A6A814586EDF}" name="CardText"/>
   </tableColumns>
@@ -16632,7 +17356,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}" name="テーブル4" displayName="テーブル4" ref="A1:C87" totalsRowShown="0">
   <autoFilter ref="A1:C87" xr:uid="{2520E7E6-995D-42A7-8B25-79B91DD52116}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{5EE7D51C-98E9-4CE6-B952-B90F83A26864}" name="ID" dataDxfId="44"/>
     <tableColumn id="2" xr3:uid="{267EEC0B-73BC-46B3-94C3-3B4B78AE4646}" name="Name"/>
     <tableColumn id="3" xr3:uid="{C293862E-7AD1-4398-868F-ACAC28AFD4D3}" name="CardText"/>
   </tableColumns>
@@ -16641,10 +17365,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}" name="テーブル5" displayName="テーブル5" ref="A1:C94" totalsRowShown="0" headerRowDxfId="43">
   <autoFilter ref="A1:C94" xr:uid="{E7B3EE24-A6DA-4A1E-8C78-02B518ABD0AA}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{F3BF1377-2632-46E6-B4F9-61BB7B20E43E}" name="ID" dataDxfId="42"/>
     <tableColumn id="1" xr3:uid="{EA68F129-90B0-48A8-AE5B-1AB69A1FED43}" name="Name"/>
     <tableColumn id="2" xr3:uid="{89C4639F-4422-47BF-AD82-8343EBF3FF95}" name="CardText"/>
   </tableColumns>
@@ -16653,60 +17377,60 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C77" totalsRowShown="0" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}" name="テーブル6" displayName="テーブル6" ref="A1:C77" totalsRowShown="0" dataDxfId="41">
   <autoFilter ref="A1:C77" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{0FD420C9-9208-48C9-A021-FE1F50D38D4A}" name="ID" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{F9E0DFA6-EAC0-4DA4-B9DB-C7E943846985}" name="Name" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{9F47887B-A27F-4689-B12B-9C74BA6BED4A}" name="CardText" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A1:C113" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CFC95865-264F-4743-B87A-3ABA9614385F}" name="テーブル68" displayName="テーブル68" ref="A1:C79" totalsRowShown="0" dataDxfId="3">
+  <autoFilter ref="A1:C79" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{D1D1406A-53A4-4F07-B7B4-50A8E2F88142}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D14DD5FC-B266-4352-A779-2B81B3B28346}" name="Name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B53E3055-C565-4468-BDC5-DE0595E65A07}" name="CardText" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="30" tableBorderDxfId="29">
-  <autoFilter ref="A1:C344" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="37" tableBorderDxfId="36">
+  <autoFilter ref="A1:C113" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
-  <autoFilter ref="A1:C126" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="32" tableBorderDxfId="31">
+  <autoFilter ref="A1:C344" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
-  <autoFilter ref="A1:C108" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+  <autoFilter ref="A1:C126" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17841,6 +18565,1388 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC80003-5833-4470-8026-FFCCC1560DD2}">
+  <dimension ref="A1:C166"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="127.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="12">
+        <v>103000</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="12">
+        <v>103001</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="12">
+        <v>103002</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="12">
+        <v>103003</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="12">
+        <v>103004</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="12">
+        <v>103005</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="12">
+        <v>103006</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="12">
+        <v>103007</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="37.5">
+      <c r="A10" s="12">
+        <v>103008</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="12">
+        <v>103009</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="12">
+        <v>103010</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="12">
+        <v>103011</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="37.5">
+      <c r="A14" s="12">
+        <v>103012</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="37.5">
+      <c r="A15" s="12">
+        <v>103013</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="12">
+        <v>103014</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="12">
+        <v>103100</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="12">
+        <v>103101</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="37.5">
+      <c r="A19" s="12">
+        <v>103102</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="37.5">
+      <c r="A20" s="12">
+        <v>103103</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="37.5">
+      <c r="A21" s="12">
+        <v>103104</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="12">
+        <v>103105</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="37.5">
+      <c r="A23" s="12">
+        <v>103106</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="12">
+        <v>103107</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="12">
+        <v>103108</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="12">
+        <v>103109</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="37.5">
+      <c r="A27" s="12">
+        <v>103110</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="37.5">
+      <c r="A28" s="12">
+        <v>103111</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="93.75">
+      <c r="A29" s="12">
+        <v>103112</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="12">
+        <v>103113</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="12">
+        <v>103200</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="12">
+        <v>103201</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="12">
+        <v>103202</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="12">
+        <v>103203</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="37.5">
+      <c r="A35" s="12">
+        <v>103204</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="12">
+        <v>103205</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="37.5">
+      <c r="A37" s="12">
+        <v>103206</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="12">
+        <v>103207</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="12">
+        <v>103208</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="12">
+        <v>103209</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="56.25">
+      <c r="A41" s="12">
+        <v>103210</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="56.25">
+      <c r="A42" s="12">
+        <v>103211</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="37.5">
+      <c r="A43" s="12">
+        <v>103212</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="12">
+        <v>103300</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="12">
+        <v>103301</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="12">
+        <v>103302</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="37.5">
+      <c r="A47" s="12">
+        <v>103303</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="37.5">
+      <c r="A48" s="12">
+        <v>103304</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="37.5">
+      <c r="A49" s="12">
+        <v>103305</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="12">
+        <v>103306</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="12">
+        <v>103307</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="37.5">
+      <c r="A52" s="12">
+        <v>103308</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="37.5">
+      <c r="A53" s="12">
+        <v>103309</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="37.5">
+      <c r="A54" s="12">
+        <v>103310</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="37.5">
+      <c r="A55" s="12">
+        <v>103311</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="37.5">
+      <c r="A56" s="12">
+        <v>103312</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="12">
+        <v>103400</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="12">
+        <v>103401</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="12">
+        <v>103402</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="12">
+        <v>103403</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="12">
+        <v>103404</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="37.5">
+      <c r="A62" s="12">
+        <v>103405</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="37.5">
+      <c r="A63" s="12">
+        <v>103406</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="37.5">
+      <c r="A64" s="12">
+        <v>103407</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="12">
+        <v>103408</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="12">
+        <v>103409</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="37.5">
+      <c r="A67" s="12">
+        <v>103410</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="37.5">
+      <c r="A68" s="12">
+        <v>103411</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="12">
+        <v>103412</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="37.5">
+      <c r="A70" s="12">
+        <v>103500</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="37.5">
+      <c r="A71" s="12">
+        <v>103501</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="37.5">
+      <c r="A72" s="12">
+        <v>103502</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="12">
+        <v>103503</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="37.5">
+      <c r="A74" s="12">
+        <v>103504</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="37.5">
+      <c r="A75" s="12">
+        <v>103505</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="12">
+        <v>103506</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="56.25">
+      <c r="A77" s="12">
+        <v>103507</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="37.5">
+      <c r="A78" s="12">
+        <v>103508</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="37.5">
+      <c r="A79" s="12">
+        <v>103509</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="37.5">
+      <c r="A80" s="12">
+        <v>103510</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="37.5">
+      <c r="A81" s="12">
+        <v>103511</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="37.5">
+      <c r="A82" s="12">
+        <v>103512</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="12">
+        <v>103600</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="37.5">
+      <c r="A84" s="12">
+        <v>103601</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="12">
+        <v>103602</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="12">
+        <v>103603</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="37.5">
+      <c r="A87" s="12">
+        <v>103604</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="37.5">
+      <c r="A88" s="12">
+        <v>103605</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="37.5">
+      <c r="A89" s="12">
+        <v>103606</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="12">
+        <v>103607</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="12">
+        <v>103608</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="37.5">
+      <c r="A92" s="12">
+        <v>103609</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="37.5">
+      <c r="A93" s="12">
+        <v>103610</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="37.5">
+      <c r="A94" s="12">
+        <v>103611</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="37.5">
+      <c r="A95" s="12">
+        <v>103612</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="12">
+        <v>103700</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="12">
+        <v>103701</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="12">
+        <v>103702</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="12">
+        <v>103703</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="12">
+        <v>103704</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="37.5">
+      <c r="A101" s="12">
+        <v>103705</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="12">
+        <v>103706</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="12">
+        <v>103707</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C103" s="23" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="37.5">
+      <c r="A104" s="12">
+        <v>103708</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C104" s="23" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="12">
+        <v>103709</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="37.5">
+      <c r="A106" s="12">
+        <v>103710</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="56.25">
+      <c r="A107" s="12">
+        <v>103711</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C107" s="23" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="75">
+      <c r="A108" s="15">
+        <v>103712</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1"/>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="1"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="1"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="1"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="1"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="1"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1"/>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="1"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="1"/>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="1"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="1"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="1"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="1"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="1"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="1"/>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="1"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1"/>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1"/>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="1"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1"/>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="1"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="1"/>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1"/>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="1"/>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B76404E-33BC-4875-8EF8-A6F76A99F78D}">
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -19222,7 +21328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F457C4E2-F844-41A5-B438-1532C7209A51}">
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -20612,7 +22718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A38EEF-C4EC-4EF1-86F2-D3A65940732E}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -20870,7 +22976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24FCBE1-754C-45D2-B30B-7C4BA5B12A85}">
   <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -21111,7 +23217,7 @@
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="25" t="s">
+      <c r="A33" t="s">
         <v>2701</v>
       </c>
     </row>
@@ -25404,7 +27510,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="75">
+    <row r="37" spans="1:3" ht="56.25">
       <c r="A37" s="12">
         <v>4309</v>
       </c>
@@ -25866,6 +27972,895 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3926E00-AF94-4788-B7CD-5D48AE98541B}">
+  <dimension ref="A1:C79"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="182" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="12">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="12">
+        <v>5001</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="12">
+        <v>5002</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="37.5">
+      <c r="A5" s="12">
+        <v>5003</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="56.25">
+      <c r="A6" s="12">
+        <v>5004</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="56.25">
+      <c r="A7" s="12">
+        <v>5005</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="37.5">
+      <c r="A8" s="12">
+        <v>5100</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="56.25">
+      <c r="A9" s="12">
+        <v>5101</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="12">
+        <v>5102</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="12">
+        <v>5103</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="56.25">
+      <c r="A12" s="12">
+        <v>5104</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="12">
+        <v>5105</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="56.25">
+      <c r="A14" s="12">
+        <v>5106</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="12">
+        <v>5107</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="37.5">
+      <c r="A16" s="12">
+        <v>5108</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="93.75">
+      <c r="A17" s="12">
+        <v>5109</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="37.5">
+      <c r="A18" s="12">
+        <v>5200</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>2777</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="12">
+        <v>5201</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="12">
+        <v>5202</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="56.25">
+      <c r="A21" s="12">
+        <v>5203</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="37.5">
+      <c r="A22" s="12">
+        <v>5204</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="37.5">
+      <c r="A23" s="12">
+        <v>5205</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="56.25">
+      <c r="A24" s="12">
+        <v>5206</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="37.5">
+      <c r="A25" s="12">
+        <v>5207</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="93.75">
+      <c r="A26" s="12">
+        <v>5208</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="12">
+        <v>5209</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="56.25">
+      <c r="A28" s="12">
+        <v>5210</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="37.5">
+      <c r="A29" s="12">
+        <v>5300</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="12">
+        <v>5301</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="12">
+        <v>5302</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="93.75">
+      <c r="A32" s="12">
+        <v>5303</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="56.25">
+      <c r="A33" s="12">
+        <v>5304</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="75">
+      <c r="A34" s="12">
+        <v>5305</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="37.5">
+      <c r="A35" s="12">
+        <v>5306</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="12">
+        <v>5307</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="93.75">
+      <c r="A37" s="12">
+        <v>5308</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="56.25">
+      <c r="A38" s="12">
+        <v>5309</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="37.5">
+      <c r="A39" s="12">
+        <v>5400</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="37.5">
+      <c r="A40" s="12">
+        <v>5401</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="12">
+        <v>5402</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="37.5">
+      <c r="A42" s="12">
+        <v>5403</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="12">
+        <v>5404</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="12">
+        <v>5405</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="12">
+        <v>5406</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="12">
+        <v>5407</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="75">
+      <c r="A47" s="12">
+        <v>5408</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="56.25">
+      <c r="A48" s="12">
+        <v>5409</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="37.5">
+      <c r="A49" s="12">
+        <v>5500</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="37.5">
+      <c r="A50" s="12">
+        <v>5501</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="12">
+        <v>5502</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="37.5">
+      <c r="A52" s="12">
+        <v>5503</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="37.5">
+      <c r="A53" s="12">
+        <v>5504</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="12">
+        <v>5505</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="56.25">
+      <c r="A55" s="12">
+        <v>5506</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="75">
+      <c r="A56" s="12">
+        <v>5507</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>2815</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="112.5">
+      <c r="A57" s="12">
+        <v>5508</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="56.25">
+      <c r="A58" s="12">
+        <v>5509</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="37.5">
+      <c r="A59" s="12">
+        <v>5600</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="56.25">
+      <c r="A60" s="12">
+        <v>5601</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="12">
+        <v>5602</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="56.25">
+      <c r="A62" s="12">
+        <v>5603</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="37.5">
+      <c r="A63" s="12">
+        <v>5604</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="12">
+        <v>5605</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="93.75">
+      <c r="A65" s="12">
+        <v>5606</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="37.5">
+      <c r="A66" s="12">
+        <v>5607</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="93.75">
+      <c r="A67" s="12">
+        <v>5608</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="93.75">
+      <c r="A68" s="12">
+        <v>5609</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="37.5">
+      <c r="A69" s="12">
+        <v>5700</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="37.5">
+      <c r="A70" s="12">
+        <v>5701</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="12">
+        <v>5702</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>2830</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="37.5">
+      <c r="A72" s="12">
+        <v>5703</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>2831</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="37.5">
+      <c r="A73" s="12">
+        <v>5704</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="12">
+        <v>5705</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="56.25">
+      <c r="A75" s="12">
+        <v>5706</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>2834</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="12">
+        <v>5707</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="56.25">
+      <c r="A77" s="12">
+        <v>5708</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="225">
+      <c r="A78" s="25">
+        <v>5709</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>2837</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
+        <v>5710</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F5E2BBB-F73A-4829-AA50-854D938D452A}">
   <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -27128,7 +30123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D209C7AA-CA9E-4A13-84F7-CB66B7ECC9E5}">
   <dimension ref="A1:C344"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -27347,7 +30342,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="37.5">
+    <row r="20" spans="1:3">
       <c r="A20" s="12">
         <v>101018</v>
       </c>
@@ -27897,7 +30892,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="37.5">
+    <row r="70" spans="1:3">
       <c r="A70" s="12">
         <v>101140</v>
       </c>
@@ -28106,7 +31101,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="37.5">
+    <row r="89" spans="1:3">
       <c r="A89" s="12">
         <v>101216</v>
       </c>
@@ -28557,7 +31552,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="37.5">
+    <row r="130" spans="1:3">
       <c r="A130" s="12">
         <v>101311</v>
       </c>
@@ -28711,7 +31706,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="37.5">
+    <row r="144" spans="1:3">
       <c r="A144" s="12">
         <v>101325</v>
       </c>
@@ -28876,7 +31871,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="37.5">
+    <row r="159" spans="1:3">
       <c r="A159" s="12">
         <v>101340</v>
       </c>
@@ -29745,7 +32740,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="37.5">
+    <row r="238" spans="1:3">
       <c r="A238" s="12">
         <v>101528</v>
       </c>
@@ -29844,7 +32839,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="37.5">
+    <row r="247" spans="1:3">
       <c r="A247" s="12">
         <v>101537</v>
       </c>
@@ -30031,7 +33026,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="37.5">
+    <row r="264" spans="1:3">
       <c r="A264" s="12">
         <v>101609</v>
       </c>
@@ -30932,7 +33927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172E6B24-33BB-45EF-9431-E259BECD3B55}">
   <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -32336,1386 +35331,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC80003-5833-4470-8026-FFCCC1560DD2}">
-  <dimension ref="A1:C166"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="127.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="12">
-        <v>103000</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1519</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="12">
-        <v>103001</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>2410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="12">
-        <v>103002</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>1521</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>2437</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="12">
-        <v>103003</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="12">
-        <v>103004</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>1523</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>2412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="12">
-        <v>103005</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>1524</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>2413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="12">
-        <v>103006</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>1525</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>2414</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="12">
-        <v>103007</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>2415</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="37.5">
-      <c r="A10" s="12">
-        <v>103008</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>1527</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>2416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="12">
-        <v>103009</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="12">
-        <v>103010</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>2417</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="12">
-        <v>103011</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>2418</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="37.5">
-      <c r="A14" s="12">
-        <v>103012</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>2419</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="37.5">
-      <c r="A15" s="12">
-        <v>103013</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>2420</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="12">
-        <v>103014</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>1533</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>2421</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="12">
-        <v>103100</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>2422</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="12">
-        <v>103101</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>1535</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>2423</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="37.5">
-      <c r="A19" s="12">
-        <v>103102</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>1536</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>2424</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="37.5">
-      <c r="A20" s="12">
-        <v>103103</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>2425</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="37.5">
-      <c r="A21" s="12">
-        <v>103104</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>2435</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="12">
-        <v>103105</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>1539</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="37.5">
-      <c r="A23" s="12">
-        <v>103106</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>2427</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="12">
-        <v>103107</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="12">
-        <v>103108</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="12">
-        <v>103109</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>1543</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="37.5">
-      <c r="A27" s="12">
-        <v>103110</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>1544</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>2431</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="37.5">
-      <c r="A28" s="12">
-        <v>103111</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>2432</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="93.75">
-      <c r="A29" s="12">
-        <v>103112</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="12">
-        <v>103113</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>1547</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="12">
-        <v>103200</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>2438</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="12">
-        <v>103201</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="12">
-        <v>103202</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="12">
-        <v>103203</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>1551</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="37.5">
-      <c r="A35" s="12">
-        <v>103204</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>1552</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="12">
-        <v>103205</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>1553</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>2442</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="37.5">
-      <c r="A37" s="12">
-        <v>103206</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="12">
-        <v>103207</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="12">
-        <v>103208</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>1556</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>2444</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="37.5">
-      <c r="A40" s="12">
-        <v>103209</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>1557</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>2445</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="56.25">
-      <c r="A41" s="12">
-        <v>103210</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>2446</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="56.25">
-      <c r="A42" s="12">
-        <v>103211</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>1559</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>2752</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="37.5">
-      <c r="A43" s="12">
-        <v>103212</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>2447</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="12">
-        <v>103300</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>1561</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>2449</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="12">
-        <v>103301</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>1562</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="12">
-        <v>103302</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>1563</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="37.5">
-      <c r="A47" s="12">
-        <v>103303</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>1564</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="37.5">
-      <c r="A48" s="12">
-        <v>103304</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>1565</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>2451</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="37.5">
-      <c r="A49" s="12">
-        <v>103305</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>1566</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>2452</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="12">
-        <v>103306</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="12">
-        <v>103307</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>1568</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>2455</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="37.5">
-      <c r="A52" s="12">
-        <v>103308</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>2456</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="37.5">
-      <c r="A53" s="12">
-        <v>103309</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>1570</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="37.5">
-      <c r="A54" s="12">
-        <v>103310</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>1571</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>2457</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="37.5">
-      <c r="A55" s="12">
-        <v>103311</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="37.5">
-      <c r="A56" s="12">
-        <v>103312</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>2459</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="12">
-        <v>103400</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="12">
-        <v>103401</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>2461</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="12">
-        <v>103402</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>2462</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="12">
-        <v>103403</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>2463</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="12">
-        <v>103404</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="37.5">
-      <c r="A62" s="12">
-        <v>103405</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>2467</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="37.5">
-      <c r="A63" s="12">
-        <v>103406</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>1580</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="37.5">
-      <c r="A64" s="12">
-        <v>103407</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>2469</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="12">
-        <v>103408</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="12">
-        <v>103409</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>1583</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>2471</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="37.5">
-      <c r="A67" s="12">
-        <v>103410</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>1584</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>2472</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="37.5">
-      <c r="A68" s="12">
-        <v>103411</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>2473</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="37.5">
-      <c r="A69" s="12">
-        <v>103412</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>1586</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="37.5">
-      <c r="A70" s="12">
-        <v>103500</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="37.5">
-      <c r="A71" s="12">
-        <v>103501</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>1588</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="37.5">
-      <c r="A72" s="12">
-        <v>103502</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>2477</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="12">
-        <v>103503</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>1590</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>2478</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="37.5">
-      <c r="A74" s="12">
-        <v>103504</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>1591</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="37.5">
-      <c r="A75" s="12">
-        <v>103505</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>1592</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>2480</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="12">
-        <v>103506</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>2481</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="56.25">
-      <c r="A77" s="12">
-        <v>103507</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C77" s="23" t="s">
-        <v>2482</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="37.5">
-      <c r="A78" s="12">
-        <v>103508</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C78" s="23" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="37.5">
-      <c r="A79" s="12">
-        <v>103509</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>1596</v>
-      </c>
-      <c r="C79" s="23" t="s">
-        <v>2485</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="37.5">
-      <c r="A80" s="12">
-        <v>103510</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>1597</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="37.5">
-      <c r="A81" s="12">
-        <v>103511</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C81" s="23" t="s">
-        <v>2487</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="37.5">
-      <c r="A82" s="12">
-        <v>103512</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="12">
-        <v>103600</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C83" s="23" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="37.5">
-      <c r="A84" s="12">
-        <v>103601</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C84" s="23" t="s">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="12">
-        <v>103602</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>1602</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="12">
-        <v>103603</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>1603</v>
-      </c>
-      <c r="C86" s="23" t="s">
-        <v>2491</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="37.5">
-      <c r="A87" s="12">
-        <v>103604</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>1604</v>
-      </c>
-      <c r="C87" s="23" t="s">
-        <v>2492</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="37.5">
-      <c r="A88" s="12">
-        <v>103605</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>2493</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="37.5">
-      <c r="A89" s="12">
-        <v>103606</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>1606</v>
-      </c>
-      <c r="C89" s="23" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="12">
-        <v>103607</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>1607</v>
-      </c>
-      <c r="C90" s="23" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="12">
-        <v>103608</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>1608</v>
-      </c>
-      <c r="C91" s="23" t="s">
-        <v>2496</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="37.5">
-      <c r="A92" s="12">
-        <v>103609</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>1609</v>
-      </c>
-      <c r="C92" s="23" t="s">
-        <v>2497</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="37.5">
-      <c r="A93" s="12">
-        <v>103610</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C93" s="23" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="37.5">
-      <c r="A94" s="12">
-        <v>103611</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C94" s="23" t="s">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="37.5">
-      <c r="A95" s="12">
-        <v>103612</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>1612</v>
-      </c>
-      <c r="C95" s="23" t="s">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="12">
-        <v>103700</v>
-      </c>
-      <c r="B96" s="11" t="s">
-        <v>1613</v>
-      </c>
-      <c r="C96" s="23" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="12">
-        <v>103701</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>1614</v>
-      </c>
-      <c r="C97" s="23" t="s">
-        <v>2753</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="12">
-        <v>103702</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C98" s="23" t="s">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="12">
-        <v>103703</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C99" s="23" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="12">
-        <v>103704</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C100" s="23" t="s">
-        <v>2505</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="37.5">
-      <c r="A101" s="12">
-        <v>103705</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>1618</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="12">
-        <v>103706</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>2517</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="12">
-        <v>103707</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>1620</v>
-      </c>
-      <c r="C103" s="23" t="s">
-        <v>2527</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="37.5">
-      <c r="A104" s="12">
-        <v>103708</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C104" s="23" t="s">
-        <v>2528</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="12">
-        <v>103709</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>1622</v>
-      </c>
-      <c r="C105" s="23" t="s">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="37.5">
-      <c r="A106" s="12">
-        <v>103710</v>
-      </c>
-      <c r="B106" s="11" t="s">
-        <v>1623</v>
-      </c>
-      <c r="C106" s="23" t="s">
-        <v>2530</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="56.25">
-      <c r="A107" s="12">
-        <v>103711</v>
-      </c>
-      <c r="B107" s="11" t="s">
-        <v>1624</v>
-      </c>
-      <c r="C107" s="23" t="s">
-        <v>2531</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="75">
-      <c r="A108" s="15">
-        <v>103712</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>2532</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="1"/>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="1"/>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="1"/>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="1"/>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="1"/>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="1"/>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="1"/>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="1"/>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="1"/>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="1"/>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="1"/>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="1"/>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1"/>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="1"/>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="1"/>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="1"/>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="1"/>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="1"/>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="1"/>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="1"/>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="1"/>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="1"/>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="1"/>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="1"/>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="1"/>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="1"/>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="1"/>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="1"/>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="1"/>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="1"/>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="1"/>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="1"/>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="1"/>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="1"/>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="1"/>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="1"/>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="1"/>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="1"/>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="1"/>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="1"/>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="1"/>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="1"/>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="1"/>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="1"/>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="1"/>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="1"/>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="1"/>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d80298dd939f2595/デスクトップ/ShadowBeyond/Assets/Resources/MasterData/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE553F7-5410-4665-8A5E-7452170534E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -16456,7 +16456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -16512,76 +16512,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="49">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="177" formatCode="000000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -17193,6 +17128,65 @@
     <dxf>
       <fill>
         <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="000000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
@@ -17305,36 +17299,36 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}" name="テーブル11" displayName="テーブル11" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:C108" xr:uid="{9E918684-E432-4F8F-97BE-B953FD0C7491}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{0C4BFE01-9BB6-4AD5-A975-FC363C6B2C12}" name="ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{50FC983C-786C-4D95-A837-F8599D3ECD3E}" name="Name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{0D0C448E-89F4-4CAD-AE15-3869E50AF6FC}" name="CardText" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{E15C51F9-F521-433C-8765-752424375382}" name="テーブル12" displayName="テーブル12" ref="A1:C108" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="A1:C108" xr:uid="{E15C51F9-F521-433C-8765-752424375382}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{A729B22F-ECC9-4B8C-958D-DA7405DF9CA5}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{52A62EF9-4070-4BD9-BF12-DC422201DF41}" name="Name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{22C96529-1489-4914-9A28-9D7ECC8D99D8}" name="CardText" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}" name="テーブル13" displayName="テーブル13" ref="A1:C109" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="A1:C109" xr:uid="{3D3562E8-02DD-400E-A6CA-034AD9E85E7A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{256812F6-8B3E-4475-8C8C-D8A633902F32}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{AC2362EA-8ECB-4E5D-AF09-4A0516EF95D3}" name="Name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{86DBF3BA-9C75-470B-A2C0-8C203D53F057}" name="CardText" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17389,48 +17383,48 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CFC95865-264F-4743-B87A-3ABA9614385F}" name="テーブル68" displayName="テーブル68" ref="A1:C79" totalsRowShown="0" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CFC95865-264F-4743-B87A-3ABA9614385F}" name="テーブル68" displayName="テーブル68" ref="A1:C79" totalsRowShown="0" dataDxfId="37">
   <autoFilter ref="A1:C79" xr:uid="{DC2C64BC-44CA-400B-B1F6-4233C9293912}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D1D1406A-53A4-4F07-B7B4-50A8E2F88142}" name="ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{D14DD5FC-B266-4352-A779-2B81B3B28346}" name="Name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B53E3055-C565-4468-BDC5-DE0595E65A07}" name="CardText" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D1D1406A-53A4-4F07-B7B4-50A8E2F88142}" name="ID" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{D14DD5FC-B266-4352-A779-2B81B3B28346}" name="Name" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{B53E3055-C565-4468-BDC5-DE0595E65A07}" name="CardText" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="37" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}" name="テーブル2" displayName="テーブル2" ref="A1:C113" totalsRowShown="0" headerRowBorderDxfId="33" tableBorderDxfId="32">
   <autoFilter ref="A1:C113" xr:uid="{2A26BC1A-8F97-4DA3-A44A-1DBB5C5EC5F1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{F998FC53-6FE5-42D4-BC5D-42D56AF0AE36}" name="ID" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{4A776E2D-6D30-419C-A7D8-C8413B275FA3}" name="Name" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{F7BF2450-2594-4F62-B8C3-906D6AAB5049}" name="CardText" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="32" tableBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}" name="テーブル8" displayName="テーブル8" ref="A1:C344" totalsRowShown="0" headerRowBorderDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A1:C344" xr:uid="{01162063-A849-4B2D-A7C7-78A3A286C65A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{3EB9556C-DBBD-4A93-9556-2ADB5B94FD95}" name="ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{15A22BAF-32A3-4C30-81B9-47A92E3B0556}" name="Name" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{B21E7F57-61CB-4FA5-9526-75E41F158C06}" name="CardText" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}" name="テーブル10" displayName="テーブル10" ref="A1:C126" totalsRowShown="0" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="A1:C126" xr:uid="{67E09ABD-372D-4DAA-BB33-9304DB949681}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{6CCBAA69-D96C-4C33-9266-6FD24FC9ADE8}" name="ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{1C80347F-14A7-4B4A-B67E-8A9AE2157257}" name="Name" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{4B199A07-0A0E-40AF-8C28-F04339D52534}" name="CardText" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28829,24 +28823,24 @@
       </c>
     </row>
     <row r="78" spans="1:3" ht="225">
-      <c r="A78" s="25">
+      <c r="A78" s="12">
         <v>5709</v>
       </c>
-      <c r="B78" s="26" t="s">
+      <c r="B78" s="11" t="s">
         <v>2837</v>
       </c>
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="6" t="s">
         <v>2914</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="25">
+      <c r="A79" s="12">
         <v>5710</v>
       </c>
-      <c r="B79" s="26" t="s">
+      <c r="B79" s="11" t="s">
         <v>2838</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" t="s">
         <v>124</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d80298dd939f2595/デスクトップ/ShadowBeyond/Assets/Resources/MasterData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaori\OneDrive\デスクトップ\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE553F7-5410-4665-8A5E-7452170534E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA66585-72B8-4412-BF2D-A38F0AC907B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5265" yWindow="3345" windowWidth="21600" windowHeight="11295" tabRatio="903" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>
@@ -23354,7 +23354,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>201</v>
@@ -23365,7 +23365,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B13" t="s">
         <v>202</v>
@@ -23376,7 +23376,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>203</v>
@@ -23387,7 +23387,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B15" t="s">
         <v>204</v>

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B00CFAE-26C2-401B-AB10-2C2A45C06E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFD3566-8494-43EF-AE4A-DAD32E7403D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BasicBeyond" sheetId="42" r:id="rId1"/>

--- a/Assets/Resources/MasterData/CardTextData.xlsx
+++ b/Assets/Resources/MasterData/CardTextData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Unity\ShadowBeyond\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFD3566-8494-43EF-AE4A-DAD32E7403D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A5394B-8EDC-4DFB-9AC5-A93EAB2D1AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
